--- a/output/model_reports/Model_Report_2025_M01.xlsx
+++ b/output/model_reports/Model_Report_2025_M01.xlsx
@@ -1032,13 +1032,13 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>5677.741</v>
+        <v>18849.353</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5677.741</v>
+        <v>18849.353</v>
       </c>
     </row>
     <row r="3">
@@ -1054,13 +1054,13 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>286777.386</v>
+        <v>234175.887</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>136438.58</v>
+        <v>130158.78</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>423215.966</v>
+        <v>364334.667</v>
       </c>
     </row>
     <row r="4">
@@ -1076,13 +1076,13 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1891.52</v>
+        <v>18619.637</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>6279.8</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1891.52</v>
+        <v>24899.437</v>
       </c>
     </row>
     <row r="5">
@@ -1142,13 +1142,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>80517.073</v>
+        <v>103218.843</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>80517.073</v>
+        <v>103218.843</v>
       </c>
     </row>
     <row r="8">
@@ -1258,31 +1258,31 @@
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>36730.81</v>
+        <v>36730.811</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>367.308</v>
+        <v>1836.541</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>34894.27</v>
+        <v>29384.648</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>1469.232</v>
+        <v>1836.541</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>0</v>
+        <v>3673.081</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.009999997277489934</v>
+        <v>0.05000001225129497</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.9500000136125503</v>
+        <v>0.7999999782199201</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.03999998910995974</v>
+        <v>0.05000001225129497</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0</v>
+        <v>0.09999999727749001</v>
       </c>
     </row>
     <row r="3">
@@ -1292,31 +1292,31 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>202921.41</v>
+        <v>202921.409</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>4058.428</v>
+        <v>10146.07</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>198862.982</v>
+        <v>152191.057</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>0</v>
+        <v>10146.07</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>0</v>
+        <v>30438.212</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.01999999901439676</v>
+        <v>0.04999999778239269</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.9800000009856034</v>
+        <v>0.7500000012320042</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0</v>
+        <v>0.04999999778239269</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0</v>
+        <v>0.1500000032032106</v>
       </c>
     </row>
     <row r="4">
@@ -1326,31 +1326,31 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>20665.2</v>
+        <v>20665.201</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>10223.067</v>
+        <v>8178.454</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>0</v>
+        <v>1022.307</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>10442.133</v>
+        <v>11464.44</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.4946996399744498</v>
+        <v>0.3957597121847496</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0</v>
+        <v>0.04946997612072585</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0.5053003600255502</v>
+        <v>0.5547703116945245</v>
       </c>
     </row>
     <row r="5">
@@ -1397,28 +1397,28 @@
         <v>70074.94</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>0</v>
+        <v>3503.747</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0</v>
+        <v>7007.494</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>0</v>
+        <v>3503.747</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>70074.94</v>
+        <v>56059.952</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1</v>
+        <v>0.7999999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1428,31 +1428,31 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>31662.75</v>
+        <v>31662.752</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>0</v>
+        <v>1583.138</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>31662.75</v>
+        <v>26913.338</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0</v>
+        <v>1583.138</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0</v>
+        <v>1583.138</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0</v>
+        <v>0.05000001263314067</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1</v>
+        <v>0.8499999621005779</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0</v>
+        <v>0.05000001263314067</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0</v>
+        <v>0.05000001263314067</v>
       </c>
     </row>
     <row r="8">
@@ -1496,28 +1496,28 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>10556.61</v>
+        <v>10556.611</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>0</v>
+        <v>527.831</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>10134.346</v>
+        <v>9500.949000000001</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>422.264</v>
+        <v>527.831</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0</v>
+        <v>0.05000004262731667</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.9600000378909518</v>
+        <v>0.8999999147453667</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.03999996210904827</v>
+        <v>0.05000004262731667</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>0</v>
@@ -1536,10 +1536,10 @@
         <v>0</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>125596.78</v>
+        <v>119316.941</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0</v>
+        <v>6279.839</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>0</v>
@@ -1548,10 +1548,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>0</v>
@@ -1801,13 +1801,13 @@
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>5677.736</v>
+        <v>18849.327</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>367.308</v>
+        <v>1836.541</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>4058.428</v>
+        <v>10146.07</v>
       </c>
       <c r="E2" s="7" t="n">
         <v>0</v>
@@ -1816,16 +1816,16 @@
         <v>1252</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>0</v>
+        <v>3503.747</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>0</v>
+        <v>1583.138</v>
       </c>
       <c r="I2" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>0</v>
+        <v>527.831</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>0</v>
@@ -1837,28 +1837,28 @@
         <v>0</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>0.0646926873669364</v>
+        <v>0.09743270940124281</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>0.7147968838283428</v>
+        <v>0.5382722682884116</v>
       </c>
       <c r="P2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>0.2205104288047208</v>
+        <v>0.0664214695835029</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>0</v>
+        <v>0.1858818089367328</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0</v>
+        <v>0.08398909945166741</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0</v>
+        <v>0.02800264433844243</v>
       </c>
       <c r="V2" s="4" t="n">
         <v>0</v>
@@ -1877,34 +1877,34 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>423215.995</v>
+        <v>364334.681</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>34894.27</v>
+        <v>29384.648</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>198862.982</v>
+        <v>152191.057</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>10223.067</v>
+        <v>8178.454</v>
       </c>
       <c r="F3" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0</v>
+        <v>7007.494</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>31662.75</v>
+        <v>26913.338</v>
       </c>
       <c r="I3" s="7" t="n">
         <v>1000</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>10134.346</v>
+        <v>9500.949000000001</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>125596.78</v>
+        <v>119316.941</v>
       </c>
       <c r="L3" s="7" t="n">
         <v>2524.8</v>
@@ -1913,37 +1913,37 @@
         <v>8317</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>0.08245026277893867</v>
+        <v>0.08065289837175836</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>0.4698853170707785</v>
+        <v>0.4177232224565522</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>0.02415567256620346</v>
+        <v>0.02244764066256981</v>
       </c>
       <c r="Q3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>0</v>
+        <v>0.01923367267910463</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.07481463454612579</v>
+        <v>0.07386982190696252</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>0.002362859655150794</v>
+        <v>0.00274472909703592</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.02394603729473882</v>
+        <v>0.02607753116975433</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0.2967675642788501</v>
+        <v>0.3274926797320182</v>
       </c>
       <c r="W3" s="4" t="n">
-        <v>0.005965748057324724</v>
+        <v>0.006929892024196292</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>0.01965190375188915</v>
+        <v>0.02282791190004775</v>
       </c>
     </row>
     <row r="4">
@@ -1953,34 +1953,34 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>1891.496</v>
+        <v>24899.473</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>1469.232</v>
+        <v>1836.541</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>0</v>
+        <v>10146.07</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>0</v>
+        <v>1022.307</v>
       </c>
       <c r="F4" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0</v>
+        <v>3503.747</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0</v>
+        <v>1583.138</v>
       </c>
       <c r="I4" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>422.264</v>
+        <v>527.831</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>0</v>
+        <v>6279.839</v>
       </c>
       <c r="L4" s="7" t="n">
         <v>0</v>
@@ -1989,31 +1989,31 @@
         <v>0</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.7767565990094613</v>
+        <v>0.07375822773437815</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0</v>
+        <v>0.4074813149659834</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>0</v>
+        <v>0.04105737498942247</v>
       </c>
       <c r="Q4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>0</v>
+        <v>0.1407157091236429</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0</v>
+        <v>0.06358118503150649</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>0.2232434009905387</v>
+        <v>0.02119848078712349</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0</v>
+        <v>0.2522077073679431</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0</v>
@@ -2029,25 +2029,25 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>80517.073</v>
+        <v>103218.823</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>0</v>
+        <v>3673.081</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>0</v>
+        <v>30438.212</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>10442.133</v>
+        <v>11464.44</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>70074.94</v>
+        <v>56059.952</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0</v>
+        <v>1583.138</v>
       </c>
       <c r="I5" s="7" t="n">
         <v>0</v>
@@ -2065,22 +2065,22 @@
         <v>0</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>0</v>
+        <v>0.03558537961627406</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>0</v>
+        <v>0.2948901287122795</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.1296884326632191</v>
+        <v>0.1110692765795246</v>
       </c>
       <c r="Q5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>0.8703115673367808</v>
+        <v>0.5431175280888447</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0</v>
+        <v>0.01533768700307695</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>0</v>
@@ -2178,25 +2178,25 @@
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>367.308</v>
+        <v>1836.541</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>34894.27</v>
+        <v>29384.648</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>1469.232</v>
+        <v>1836.541</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>0</v>
+        <v>3673.081</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>36730.81</v>
+        <v>36730.811</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>36730.81</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.9500000136125503</v>
+        <v>0.7999999782199201</v>
       </c>
     </row>
     <row r="3">
@@ -2206,25 +2206,25 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>4058.428</v>
+        <v>10146.07</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>198862.982</v>
+        <v>152191.057</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>0</v>
+        <v>10146.07</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>0</v>
+        <v>30438.212</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>202921.41</v>
+        <v>202921.409</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>202921.41</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.9800000009856034</v>
+        <v>0.7500000012320042</v>
       </c>
     </row>
     <row r="4">
@@ -2237,22 +2237,22 @@
         <v>0</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>10223.067</v>
+        <v>8178.454</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>0</v>
+        <v>1022.307</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>10442.133</v>
+        <v>11464.44</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>20665.2</v>
+        <v>20665.201</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>20665.2</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.4946996399744498</v>
+        <v>0.3957597121847496</v>
       </c>
     </row>
     <row r="5">
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>0</v>
+        <v>3503.747</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>0</v>
+        <v>7007.494</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0</v>
+        <v>3503.747</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>70074.94</v>
+        <v>56059.952</v>
       </c>
       <c r="F6" s="7" t="n">
         <v>70074.94</v>
@@ -2308,7 +2308,7 @@
         <v>70074.94</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0</v>
+        <v>0.09999999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2318,25 +2318,25 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>0</v>
+        <v>1583.138</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>31662.75</v>
+        <v>26913.338</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0</v>
+        <v>1583.138</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0</v>
+        <v>1583.138</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>31662.75</v>
+        <v>31662.752</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>31662.75</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1</v>
+        <v>0.8499999621005779</v>
       </c>
     </row>
     <row r="8">
@@ -2374,25 +2374,25 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0</v>
+        <v>527.831</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>10134.346</v>
+        <v>9500.949000000001</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>422.264</v>
+        <v>527.831</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>10556.61</v>
+        <v>10556.611</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>10556.61</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.9600000378909518</v>
+        <v>0.8999999147453667</v>
       </c>
     </row>
     <row r="10">
@@ -2405,10 +2405,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>125596.78</v>
+        <v>119316.941</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0</v>
+        <v>6279.839</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
@@ -2420,7 +2420,7 @@
         <v>125596.78</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1</v>
+        <v>0.9500000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -2486,19 +2486,19 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>5677.736</v>
+        <v>18849.327</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>423215.995</v>
+        <v>364334.681</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>1891.496</v>
+        <v>24899.473</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>80517.073</v>
+        <v>103218.823</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>511302.3</v>
+        <v>511302.304</v>
       </c>
       <c r="G13" s="8" t="n">
         <v>511302.3</v>
@@ -2623,13 +2623,13 @@
         <v>18233.212</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>18870.434</v>
+        <v>16807.94</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>32632.213</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>16216.78</v>
+        <v>15310.8</v>
       </c>
       <c r="L2" t="inlineStr"/>
     </row>
@@ -2663,13 +2663,13 @@
         <v>10934.843</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>11313.941</v>
+        <v>9875.009</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>17735.28</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>7684.591</v>
+        <v>7486.723</v>
       </c>
       <c r="L3" t="inlineStr"/>
     </row>
@@ -2703,13 +2703,13 @@
         <v>3649.647</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3778.988</v>
+        <v>3485.077</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>7605.273</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>4467.156</v>
+        <v>4081.493</v>
       </c>
       <c r="L4" t="inlineStr"/>
     </row>
@@ -2743,13 +2743,13 @@
         <v>3647.304</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3775.162</v>
+        <v>3387.721</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>6774.365</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>3518.056</v>
+        <v>3292.392</v>
       </c>
       <c r="L5" t="inlineStr"/>
     </row>
@@ -2783,13 +2783,13 @@
         <v>3646.956</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3774.594</v>
+        <v>3373.406</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>6648.202</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>3376.814</v>
+        <v>3174.818</v>
       </c>
       <c r="L6" t="inlineStr"/>
     </row>
@@ -2823,13 +2823,13 @@
         <v>3645.885</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>3772.845</v>
+        <v>3328.236</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>6243.998</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2942.812</v>
+        <v>2814.981</v>
       </c>
       <c r="L7" t="inlineStr"/>
     </row>
@@ -2863,13 +2863,13 @@
         <v>3061.556</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3148.503</v>
+        <v>2867.791</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>6122.045</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>3442.55</v>
+        <v>3174.638</v>
       </c>
       <c r="L8" t="inlineStr"/>
     </row>
@@ -2903,13 +2903,13 @@
         <v>2661.555</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3235.955</v>
+        <v>2865.518</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>3667.782</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>2154.839</v>
+        <v>2113.596</v>
       </c>
       <c r="L9" t="inlineStr"/>
     </row>
@@ -2943,13 +2943,13 @@
         <v>2235.628</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2700.163</v>
+        <v>3016.762</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>8964.673000000001</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>10211.933</v>
+        <v>8982.569</v>
       </c>
       <c r="L10" t="inlineStr"/>
     </row>
@@ -2983,13 +2983,13 @@
         <v>939.573</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1150.781</v>
+        <v>1312.081</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>4054.36</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>4678.238</v>
+        <v>4107.195</v>
       </c>
       <c r="L11" t="inlineStr"/>
     </row>
@@ -3023,13 +3023,13 @@
         <v>787.827</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>914.25</v>
+        <v>952.566</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>2424.419</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>2611.446</v>
+        <v>2318.077</v>
       </c>
       <c r="L12" t="inlineStr"/>
     </row>
@@ -3063,13 +3063,13 @@
         <v>777.678</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>902</v>
+        <v>841.212</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1465.633</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1257.431</v>
+        <v>1155.567</v>
       </c>
       <c r="L13" t="inlineStr"/>
     </row>
@@ -3103,13 +3103,13 @@
         <v>697.468</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1118.988</v>
+        <v>1640.405</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>6812.267</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>8773.546</v>
+        <v>7587.009</v>
       </c>
       <c r="L14" t="inlineStr"/>
     </row>
@@ -3143,13 +3143,13 @@
         <v>677.96</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1087.132</v>
+        <v>1014.756</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>1509.059</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>821.5359999999999</v>
+        <v>769.27</v>
       </c>
       <c r="L15" t="inlineStr"/>
     </row>
@@ -3183,13 +3183,13 @@
         <v>657.741</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>742.224</v>
+        <v>782.0599999999999</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>2246.368</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1862.817</v>
+        <v>1626.919</v>
       </c>
       <c r="L16" t="inlineStr"/>
     </row>
@@ -3223,13 +3223,13 @@
         <v>597.723</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>646.212</v>
+        <v>1018.817</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>5017.485</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>4928.679</v>
+        <v>4151.76</v>
       </c>
       <c r="L17" t="inlineStr"/>
     </row>
@@ -3263,13 +3263,13 @@
         <v>530.367</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>530.367</v>
+        <v>424.294</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>413.686</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>53.037</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -3307,13 +3307,13 @@
         <v>418.481</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>671.3920000000001</v>
+        <v>984.242</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>4087.36</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>5264.128</v>
+        <v>4552.206</v>
       </c>
       <c r="L19" t="inlineStr"/>
     </row>
@@ -3347,13 +3347,13 @@
         <v>406.554</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>651.9160000000001</v>
+        <v>600.601</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>827.372</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>403.265</v>
+        <v>386.074</v>
       </c>
       <c r="L20" t="inlineStr"/>
     </row>
@@ -3387,13 +3387,13 @@
         <v>356.026</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>398.052</v>
+        <v>386.863</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>795.865</v>
+        <v>717.511</v>
       </c>
       <c r="L21" t="inlineStr"/>
     </row>
@@ -3427,13 +3427,13 @@
         <v>356.026</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>398.052</v>
+        <v>386.863</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>795.865</v>
+        <v>717.511</v>
       </c>
       <c r="L22" t="inlineStr"/>
     </row>
@@ -3467,13 +3467,13 @@
         <v>279.968</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>449.196</v>
+        <v>721.438</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>3045.591</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>3893.443</v>
+        <v>3327.504</v>
       </c>
       <c r="L23" t="inlineStr"/>
     </row>
@@ -3507,13 +3507,13 @@
         <v>265.183</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>265.183</v>
+        <v>212.146</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>206.842</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>26.519</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -3551,13 +3551,13 @@
         <v>265.183</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>265.183</v>
+        <v>212.146</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>206.842</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>26.519</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -3595,13 +3595,13 @@
         <v>265.183</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>265.183</v>
+        <v>212.146</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>206.842</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>26.519</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -3639,13 +3639,13 @@
         <v>265.183</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>265.183</v>
+        <v>212.146</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>206.842</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>26.519</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -3683,13 +3683,13 @@
         <v>265.183</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>265.183</v>
+        <v>212.146</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>206.842</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>26.519</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -3727,13 +3727,13 @@
         <v>265.183</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>265.183</v>
+        <v>212.146</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>206.842</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>26.519</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -3771,13 +3771,13 @@
         <v>212.712</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>341.366</v>
+        <v>603.782</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>3025.502</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>4047.143</v>
+        <v>3488.909</v>
       </c>
       <c r="L30" t="inlineStr"/>
     </row>
@@ -3811,13 +3811,13 @@
         <v>211.641</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>339.617</v>
+        <v>587.37</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>2745.05</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>3602.056</v>
+        <v>3087.994</v>
       </c>
       <c r="L31" t="inlineStr"/>
     </row>
@@ -3851,13 +3851,13 @@
         <v>210.014</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>336.96</v>
+        <v>516.0309999999999</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>2266.489</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>2948.361</v>
+        <v>2549.288</v>
       </c>
       <c r="L32" t="inlineStr"/>
     </row>
@@ -3891,13 +3891,13 @@
         <v>141.83</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>227.612</v>
+        <v>403.239</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>2023.697</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>2706.83</v>
+        <v>2333.427</v>
       </c>
       <c r="L33" t="inlineStr"/>
     </row>
@@ -3931,13 +3931,13 @@
         <v>141.83</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>227.612</v>
+        <v>403.239</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>2023.697</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>2706.83</v>
+        <v>2333.427</v>
       </c>
       <c r="L34" t="inlineStr"/>
     </row>
@@ -3971,13 +3971,13 @@
         <v>141.829</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>227.611</v>
+        <v>403.238</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>2023.697</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>2706.831</v>
+        <v>2333.428</v>
       </c>
       <c r="L35" t="inlineStr"/>
     </row>
@@ -4011,13 +4011,13 @@
         <v>141.184</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>226.558</v>
+        <v>382.577</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>1843.427</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>2443.682</v>
+        <v>2107.899</v>
       </c>
       <c r="L36" t="inlineStr"/>
     </row>
@@ -4051,13 +4051,13 @@
         <v>140.758</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>225.862</v>
+        <v>386.076</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>1743.247</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2262.097</v>
+        <v>1933.621</v>
       </c>
       <c r="L37" t="inlineStr"/>
     </row>
@@ -4091,13 +4091,13 @@
         <v>140.693</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>225.756</v>
+        <v>383.97</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>1723.157</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2235.867</v>
+        <v>1911.093</v>
       </c>
       <c r="L38" t="inlineStr"/>
     </row>
@@ -4131,13 +4131,13 @@
         <v>140.629</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>225.651</v>
+        <v>381.865</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>1703.067</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>2209.638</v>
+        <v>1888.565</v>
       </c>
       <c r="L39" t="inlineStr"/>
     </row>
@@ -4171,13 +4171,13 @@
         <v>140.475</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>225.399</v>
+        <v>359.761</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>1643.065</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>2154.334</v>
+        <v>1859.911</v>
       </c>
       <c r="L40" t="inlineStr"/>
     </row>
@@ -4211,13 +4211,13 @@
         <v>140.475</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>225.399</v>
+        <v>374.954</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>1660.745</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>2147.285</v>
+        <v>1837.384</v>
       </c>
       <c r="L41" t="inlineStr"/>
     </row>
@@ -4251,13 +4251,13 @@
         <v>140.41</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>225.294</v>
+        <v>372.847</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>1640.656</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2121.055</v>
+        <v>1814.86</v>
       </c>
       <c r="L42" t="inlineStr"/>
     </row>
@@ -4291,13 +4291,13 @@
         <v>140.41</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>225.294</v>
+        <v>357.61</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>1622.976</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2128.131</v>
+        <v>1837.45</v>
       </c>
       <c r="L43" t="inlineStr"/>
     </row>
@@ -4331,13 +4331,13 @@
         <v>140.41</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>225.294</v>
+        <v>357.61</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>1622.976</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>2128.131</v>
+        <v>1837.45</v>
       </c>
       <c r="L44" t="inlineStr"/>
     </row>
@@ -4371,13 +4371,13 @@
         <v>140.409</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>225.293</v>
+        <v>357.609</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>1622.976</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>2128.132</v>
+        <v>1837.451</v>
       </c>
       <c r="L45" t="inlineStr"/>
     </row>
@@ -4411,13 +4411,13 @@
         <v>139.623</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>224.008</v>
+        <v>362.011</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>1442.705</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1793.373</v>
+        <v>1518.393</v>
       </c>
       <c r="L46" t="inlineStr"/>
     </row>
@@ -4451,13 +4451,13 @@
         <v>139.557</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>223.901</v>
+        <v>359.887</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>1422.616</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>1767.145</v>
+        <v>1495.896</v>
       </c>
       <c r="L47" t="inlineStr"/>
     </row>
@@ -4491,13 +4491,13 @@
         <v>139.557</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>223.901</v>
+        <v>359.887</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>1422.616</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1767.145</v>
+        <v>1495.896</v>
       </c>
       <c r="L48" t="inlineStr"/>
     </row>
@@ -4531,13 +4531,13 @@
         <v>139.493</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>223.796</v>
+        <v>328.08</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>1362.453</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1754.71</v>
+        <v>1517.402</v>
       </c>
       <c r="L49" t="inlineStr"/>
     </row>
@@ -4571,13 +4571,13 @@
         <v>138.989</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>222.974</v>
+        <v>337.727</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>1257.613</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1537.483</v>
+        <v>1303.301</v>
       </c>
       <c r="L50" t="inlineStr"/>
     </row>
@@ -4611,13 +4611,13 @@
         <v>137.26</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>220.15</v>
+        <v>270.904</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>887.725</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>838.471</v>
+        <v>715.107</v>
       </c>
       <c r="L51" t="inlineStr"/>
     </row>
@@ -4651,13 +4651,13 @@
         <v>136.379</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>218.711</v>
+        <v>234.022</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>576.775</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>482.56</v>
+        <v>419.962</v>
       </c>
       <c r="L52" t="inlineStr"/>
     </row>
@@ -4691,13 +4691,13 @@
         <v>135.518</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>217.305</v>
+        <v>200.2</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>275.79</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>134.422</v>
+        <v>128.691</v>
       </c>
       <c r="L53" t="inlineStr"/>
     </row>
@@ -4731,13 +4731,13 @@
         <v>135.518</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>217.305</v>
+        <v>200.2</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>275.79</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>134.422</v>
+        <v>128.691</v>
       </c>
       <c r="L54" t="inlineStr"/>
     </row>
@@ -4771,13 +4771,13 @@
         <v>135.517</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>217.304</v>
+        <v>200.199</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>275.79</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>134.423</v>
+        <v>128.692</v>
       </c>
       <c r="L55" t="inlineStr"/>
     </row>
@@ -4811,13 +4811,13 @@
         <v>72.57299999999999</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>116.514</v>
+        <v>267.015</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>1560.564</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>2022.082</v>
+        <v>1725.561</v>
       </c>
       <c r="L56" t="inlineStr"/>
     </row>
@@ -4851,13 +4851,13 @@
         <v>72.283</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>116.04</v>
+        <v>255.113</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>1462.795</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1905.205</v>
+        <v>1628.537</v>
       </c>
       <c r="L57" t="inlineStr"/>
     </row>
@@ -4891,13 +4891,13 @@
         <v>71.366</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>114.543</v>
+        <v>221.15</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>1167.21</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1535.53</v>
+        <v>1317.142</v>
       </c>
       <c r="L58" t="inlineStr"/>
     </row>
@@ -4931,13 +4931,13 @@
         <v>71.309</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>114.449</v>
+        <v>216.013</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>1172.164</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1514.144</v>
+        <v>1302.234</v>
       </c>
       <c r="L59" t="inlineStr"/>
     </row>
@@ -4971,13 +4971,13 @@
         <v>71.03400000000001</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>114.001</v>
+        <v>205.588</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>1048.871</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1401.699</v>
+        <v>1208.103</v>
       </c>
       <c r="L60" t="inlineStr"/>
     </row>
@@ -5011,13 +5011,13 @@
         <v>70.947</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>113.859</v>
+        <v>202.696</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1366.514</v>
+        <v>1177.943</v>
       </c>
       <c r="L61" t="inlineStr"/>
     </row>
@@ -5051,13 +5051,13 @@
         <v>70.947</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>113.859</v>
+        <v>202.696</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1366.514</v>
+        <v>1177.943</v>
       </c>
       <c r="L62" t="inlineStr"/>
     </row>
@@ -5091,13 +5091,13 @@
         <v>70.947</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>113.859</v>
+        <v>202.696</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1366.514</v>
+        <v>1177.943</v>
       </c>
       <c r="L63" t="inlineStr"/>
     </row>
@@ -5131,13 +5131,13 @@
         <v>70.947</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>113.859</v>
+        <v>202.696</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1366.514</v>
+        <v>1177.943</v>
       </c>
       <c r="L64" t="inlineStr"/>
     </row>
@@ -5171,13 +5171,13 @@
         <v>70.947</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>113.859</v>
+        <v>202.696</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1366.514</v>
+        <v>1177.943</v>
       </c>
       <c r="L65" t="inlineStr"/>
     </row>
@@ -5211,13 +5211,13 @@
         <v>70.947</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>113.859</v>
+        <v>202.696</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1366.514</v>
+        <v>1177.943</v>
       </c>
       <c r="L66" t="inlineStr"/>
     </row>
@@ -5251,13 +5251,13 @@
         <v>70.947</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>113.859</v>
+        <v>202.696</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1366.514</v>
+        <v>1177.943</v>
       </c>
       <c r="L67" t="inlineStr"/>
     </row>
@@ -5291,13 +5291,13 @@
         <v>70.947</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>113.859</v>
+        <v>202.696</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1366.514</v>
+        <v>1177.943</v>
       </c>
       <c r="L68" t="inlineStr"/>
     </row>
@@ -5331,13 +5331,13 @@
         <v>70.947</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>113.859</v>
+        <v>202.696</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1366.514</v>
+        <v>1177.943</v>
       </c>
       <c r="L69" t="inlineStr"/>
     </row>
@@ -5371,13 +5371,13 @@
         <v>70.947</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>113.859</v>
+        <v>202.696</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1366.514</v>
+        <v>1177.943</v>
       </c>
       <c r="L70" t="inlineStr"/>
     </row>
@@ -5411,13 +5411,13 @@
         <v>70.947</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>113.859</v>
+        <v>202.696</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1366.514</v>
+        <v>1177.943</v>
       </c>
       <c r="L71" t="inlineStr"/>
     </row>
@@ -5451,13 +5451,13 @@
         <v>70.947</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>113.858</v>
+        <v>202.695</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1366.514</v>
+        <v>1177.943</v>
       </c>
       <c r="L72" t="inlineStr"/>
     </row>
@@ -5491,13 +5491,13 @@
         <v>70.947</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>113.858</v>
+        <v>202.695</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1366.514</v>
+        <v>1177.943</v>
       </c>
       <c r="L73" t="inlineStr"/>
     </row>
@@ -5531,13 +5531,13 @@
         <v>70.947</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>113.859</v>
+        <v>202.696</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1366.514</v>
+        <v>1177.943</v>
       </c>
       <c r="L74" t="inlineStr"/>
     </row>
@@ -5571,13 +5571,13 @@
         <v>70.947</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>113.858</v>
+        <v>202.695</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>1366.514</v>
+        <v>1177.943</v>
       </c>
       <c r="L75" t="inlineStr"/>
     </row>
@@ -5611,13 +5611,13 @@
         <v>70.947</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>113.858</v>
+        <v>202.695</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1366.514</v>
+        <v>1177.943</v>
       </c>
       <c r="L76" t="inlineStr"/>
     </row>
@@ -5651,13 +5651,13 @@
         <v>70.947</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>113.858</v>
+        <v>202.695</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1366.514</v>
+        <v>1177.943</v>
       </c>
       <c r="L77" t="inlineStr"/>
     </row>
@@ -5691,13 +5691,13 @@
         <v>70.947</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>113.858</v>
+        <v>202.695</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>1366.514</v>
+        <v>1177.943</v>
       </c>
       <c r="L78" t="inlineStr"/>
     </row>
@@ -5731,13 +5731,13 @@
         <v>70.947</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>113.859</v>
+        <v>202.696</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>1366.514</v>
+        <v>1177.943</v>
       </c>
       <c r="L79" t="inlineStr"/>
     </row>
@@ -5771,13 +5771,13 @@
         <v>70.947</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>113.859</v>
+        <v>202.696</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>1366.514</v>
+        <v>1177.943</v>
       </c>
       <c r="L80" t="inlineStr"/>
     </row>
@@ -5811,13 +5811,13 @@
         <v>70.88200000000001</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>113.753</v>
+        <v>200.542</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>1001.804</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1340.315</v>
+        <v>1155.484</v>
       </c>
       <c r="L81" t="inlineStr"/>
     </row>
@@ -5851,13 +5851,13 @@
         <v>70.592</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>113.279</v>
+        <v>196.081</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>946.758</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1220.016</v>
+        <v>1046.845</v>
       </c>
       <c r="L82" t="inlineStr"/>
     </row>
@@ -5891,13 +5891,13 @@
         <v>70.53</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>113.177</v>
+        <v>210.627</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>972.247</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>1186.895</v>
+        <v>1000.474</v>
       </c>
       <c r="L83" t="inlineStr"/>
     </row>
@@ -5931,13 +5931,13 @@
         <v>70.23699999999999</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>112.699</v>
+        <v>179.88</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>1077.167</v>
+        <v>929.956</v>
       </c>
       <c r="L84" t="inlineStr"/>
     </row>
@@ -5971,13 +5971,13 @@
         <v>70.23699999999999</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>112.699</v>
+        <v>179.88</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>1077.167</v>
+        <v>929.956</v>
       </c>
       <c r="L85" t="inlineStr"/>
     </row>
@@ -6011,13 +6011,13 @@
         <v>70.23699999999999</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>112.699</v>
+        <v>179.88</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>1077.167</v>
+        <v>929.956</v>
       </c>
       <c r="L86" t="inlineStr"/>
     </row>
@@ -6051,13 +6051,13 @@
         <v>70.23699999999999</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>112.699</v>
+        <v>179.88</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1077.167</v>
+        <v>929.956</v>
       </c>
       <c r="L87" t="inlineStr"/>
     </row>
@@ -6091,13 +6091,13 @@
         <v>70.23699999999999</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>112.699</v>
+        <v>179.88</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>1077.167</v>
+        <v>929.956</v>
       </c>
       <c r="L88" t="inlineStr"/>
     </row>
@@ -6131,13 +6131,13 @@
         <v>70.23699999999999</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>112.698</v>
+        <v>179.879</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>1077.168</v>
+        <v>929.957</v>
       </c>
       <c r="L89" t="inlineStr"/>
     </row>
@@ -6171,13 +6171,13 @@
         <v>70.23699999999999</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>112.698</v>
+        <v>179.879</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1077.168</v>
+        <v>929.957</v>
       </c>
       <c r="L90" t="inlineStr"/>
     </row>
@@ -6211,13 +6211,13 @@
         <v>70.23699999999999</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>112.698</v>
+        <v>179.879</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>1077.168</v>
+        <v>929.957</v>
       </c>
       <c r="L91" t="inlineStr"/>
     </row>
@@ -6251,13 +6251,13 @@
         <v>70.23699999999999</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>112.699</v>
+        <v>179.88</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1077.167</v>
+        <v>929.956</v>
       </c>
       <c r="L92" t="inlineStr"/>
     </row>
@@ -6291,13 +6291,13 @@
         <v>70.23699999999999</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>112.699</v>
+        <v>179.88</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1077.167</v>
+        <v>929.956</v>
       </c>
       <c r="L93" t="inlineStr"/>
     </row>
@@ -6331,13 +6331,13 @@
         <v>70.23699999999999</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>112.699</v>
+        <v>179.88</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1077.167</v>
+        <v>929.956</v>
       </c>
       <c r="L94" t="inlineStr"/>
     </row>
@@ -6371,13 +6371,13 @@
         <v>70.173</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>112.595</v>
+        <v>177.729</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>801.444</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1050.964</v>
+        <v>907.494</v>
       </c>
       <c r="L95" t="inlineStr"/>
     </row>
@@ -6411,13 +6411,13 @@
         <v>69.86</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>112.084</v>
+        <v>168.207</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>728.371</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>923.67</v>
+        <v>797.71</v>
       </c>
       <c r="L96" t="inlineStr"/>
     </row>
@@ -6451,13 +6451,13 @@
         <v>69.81100000000001</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>112.004</v>
+        <v>181.005</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>721.353</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>896.686</v>
+        <v>759.197</v>
       </c>
       <c r="L97" t="inlineStr"/>
     </row>
@@ -6491,13 +6491,13 @@
         <v>69.81100000000001</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>112.004</v>
+        <v>181.005</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>721.353</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>896.686</v>
+        <v>759.197</v>
       </c>
       <c r="L98" t="inlineStr"/>
     </row>
@@ -6531,13 +6531,13 @@
         <v>69.81100000000001</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>112.004</v>
+        <v>181.005</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>721.353</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>896.686</v>
+        <v>759.197</v>
       </c>
       <c r="L99" t="inlineStr"/>
     </row>
@@ -6571,13 +6571,13 @@
         <v>69.81100000000001</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>112.004</v>
+        <v>181.005</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>721.353</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>896.686</v>
+        <v>759.197</v>
       </c>
       <c r="L100" t="inlineStr"/>
     </row>
@@ -6611,13 +6611,13 @@
         <v>69.81100000000001</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>112.003</v>
+        <v>181.004</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>721.353</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>896.687</v>
+        <v>759.198</v>
       </c>
       <c r="L101" t="inlineStr"/>
     </row>
@@ -6651,13 +6651,13 @@
         <v>69.81100000000001</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>112.003</v>
+        <v>181.004</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>721.353</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>896.687</v>
+        <v>759.198</v>
       </c>
       <c r="L102" t="inlineStr"/>
     </row>
@@ -6691,13 +6691,13 @@
         <v>69.747</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>111.899</v>
+        <v>164.041</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>681.226</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>877.354</v>
+        <v>758.701</v>
       </c>
       <c r="L103" t="inlineStr"/>
     </row>
@@ -6731,13 +6731,13 @@
         <v>69.747</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>111.898</v>
+        <v>178.883</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>701.2619999999999</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>870.457</v>
+        <v>736.698</v>
       </c>
       <c r="L104" t="inlineStr"/>
     </row>
@@ -6771,13 +6771,13 @@
         <v>69.747</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>111.898</v>
+        <v>164.04</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>681.226</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>877.355</v>
+        <v>758.702</v>
       </c>
       <c r="L105" t="inlineStr"/>
     </row>
@@ -6811,13 +6811,13 @@
         <v>69.527</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>111.54</v>
+        <v>169.928</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>638.851</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>781.856</v>
+        <v>662.896</v>
       </c>
       <c r="L106" t="inlineStr"/>
     </row>
@@ -6851,13 +6851,13 @@
         <v>69.527</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>111.539</v>
+        <v>169.927</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>638.851</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>781.857</v>
+        <v>662.896</v>
       </c>
       <c r="L107" t="inlineStr"/>
     </row>
@@ -6891,13 +6891,13 @@
         <v>69.527</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>111.539</v>
+        <v>169.927</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>638.851</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>781.857</v>
+        <v>662.896</v>
       </c>
       <c r="L108" t="inlineStr"/>
     </row>
@@ -6931,13 +6931,13 @@
         <v>69.5</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>111.496</v>
+        <v>167.317</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>720.927</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>770.9829999999999</v>
+        <v>654.372</v>
       </c>
       <c r="L109" t="inlineStr"/>
     </row>
@@ -6971,13 +6971,13 @@
         <v>69.14</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>110.907</v>
+        <v>144.069</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>584.207</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>630.317</v>
+        <v>546.828</v>
       </c>
       <c r="L110" t="inlineStr"/>
     </row>
@@ -7011,13 +7011,13 @@
         <v>68.946</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>110.591</v>
+        <v>148.248</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>554.088</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>546.949</v>
+        <v>464.015</v>
       </c>
       <c r="L111" t="inlineStr"/>
     </row>
@@ -7051,13 +7051,13 @@
         <v>68.804</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>110.358</v>
+        <v>142.533</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>503.997</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>489.668</v>
+        <v>416.236</v>
       </c>
       <c r="L112" t="inlineStr"/>
     </row>
@@ -7091,13 +7091,13 @@
         <v>68.64</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>110.091</v>
+        <v>128.021</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>379.829</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>426.952</v>
+        <v>373.353</v>
       </c>
       <c r="L113" t="inlineStr"/>
     </row>
@@ -7131,13 +7131,13 @@
         <v>68.114</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>109.232</v>
+        <v>111.375</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>252.808</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>211.962</v>
+        <v>188.369</v>
       </c>
       <c r="L114" t="inlineStr"/>
     </row>
@@ -7171,13 +7171,13 @@
         <v>68.114</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>109.232</v>
+        <v>114.429</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>263.121</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>210.777</v>
+        <v>183.976</v>
       </c>
       <c r="L115" t="inlineStr"/>
     </row>
@@ -7211,13 +7211,13 @@
         <v>68.107</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>109.22</v>
+        <v>111.131</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>225.004</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>209.482</v>
+        <v>186.627</v>
       </c>
       <c r="L116" t="inlineStr"/>
     </row>
@@ -7251,13 +7251,13 @@
         <v>67.97199999999999</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>109.001</v>
+        <v>108.319</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>213.03</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>153.376</v>
+        <v>136.59</v>
       </c>
       <c r="L117" t="inlineStr"/>
     </row>
@@ -7291,13 +7291,13 @@
         <v>67.97199999999999</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>109</v>
+        <v>108.318</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>213.03</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>153.377</v>
+        <v>136.591</v>
       </c>
       <c r="L118" t="inlineStr"/>
     </row>
@@ -7331,13 +7331,13 @@
         <v>67.97199999999999</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>109.001</v>
+        <v>108.572</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>213.03</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>153.398</v>
+        <v>136.305</v>
       </c>
       <c r="L119" t="inlineStr"/>
     </row>
@@ -7371,13 +7371,13 @@
         <v>67.759</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>108.653</v>
+        <v>100.1</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>67.211</v>
+        <v>64.346</v>
       </c>
       <c r="L120" t="inlineStr"/>
     </row>
@@ -7411,13 +7411,13 @@
         <v>67.759</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>108.653</v>
+        <v>100.1</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>67.211</v>
+        <v>64.346</v>
       </c>
       <c r="L121" t="inlineStr"/>
     </row>
@@ -7451,13 +7451,13 @@
         <v>67.759</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>108.653</v>
+        <v>100.1</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>67.211</v>
+        <v>64.346</v>
       </c>
       <c r="L122" t="inlineStr"/>
     </row>
@@ -7491,13 +7491,13 @@
         <v>67.759</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>108.653</v>
+        <v>100.1</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>67.211</v>
+        <v>64.346</v>
       </c>
       <c r="L123" t="inlineStr"/>
     </row>
@@ -7531,13 +7531,13 @@
         <v>67.759</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>108.652</v>
+        <v>100.099</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>67.212</v>
+        <v>64.34699999999999</v>
       </c>
       <c r="L124" t="inlineStr"/>
     </row>
@@ -7571,13 +7571,13 @@
         <v>67.759</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>108.652</v>
+        <v>100.099</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>67.212</v>
+        <v>64.34699999999999</v>
       </c>
       <c r="L125" t="inlineStr"/>
     </row>
@@ -7611,13 +7611,13 @@
         <v>67.759</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>108.652</v>
+        <v>100.099</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>67.212</v>
+        <v>64.34699999999999</v>
       </c>
       <c r="L126" t="inlineStr"/>
     </row>
@@ -7651,13 +7651,13 @@
         <v>67.759</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>108.652</v>
+        <v>100.099</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>67.212</v>
+        <v>64.34699999999999</v>
       </c>
       <c r="L127" t="inlineStr"/>
     </row>
@@ -7691,13 +7691,13 @@
         <v>67.759</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>108.652</v>
+        <v>100.099</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>67.212</v>
+        <v>64.34699999999999</v>
       </c>
       <c r="L128" t="inlineStr"/>
     </row>
@@ -7731,13 +7731,13 @@
         <v>67.759</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>108.652</v>
+        <v>100.099</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>67.212</v>
+        <v>64.34699999999999</v>
       </c>
       <c r="L129" t="inlineStr"/>
     </row>
@@ -7771,13 +7771,13 @@
         <v>67.759</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>108.653</v>
+        <v>100.1</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>67.211</v>
+        <v>64.346</v>
       </c>
       <c r="L130" t="inlineStr"/>
     </row>
@@ -7811,13 +7811,13 @@
         <v>67.759</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>108.653</v>
+        <v>100.1</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>67.211</v>
+        <v>64.346</v>
       </c>
       <c r="L131" t="inlineStr"/>
     </row>
@@ -7851,13 +7851,13 @@
         <v>67.759</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>108.653</v>
+        <v>100.1</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>67.211</v>
+        <v>64.346</v>
       </c>
       <c r="L132" t="inlineStr"/>
     </row>
@@ -7891,13 +7891,13 @@
         <v>67.759</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>108.653</v>
+        <v>100.1</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>67.211</v>
+        <v>64.346</v>
       </c>
       <c r="L133" t="inlineStr"/>
     </row>
@@ -7931,13 +7931,13 @@
         <v>0</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0</v>
+        <v>53.218</v>
       </c>
       <c r="J134" s="2" t="n">
         <v>540.143</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>664.377</v>
+        <v>565.776</v>
       </c>
       <c r="L134" t="inlineStr"/>
     </row>
@@ -7971,13 +7971,13 @@
         <v>0</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>0</v>
+        <v>22.321</v>
       </c>
       <c r="J135" s="2" t="n">
         <v>213.326</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>230.866</v>
+        <v>192.327</v>
       </c>
       <c r="L135" t="inlineStr"/>
     </row>
@@ -7992,7 +7992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -8044,7 +8044,7 @@
         <v>1826.525</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>242.561</v>
+        <v>1552.786</v>
       </c>
     </row>
     <row r="4">
@@ -8057,7 +8057,7 @@
         <v>5898.341</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>11938.851</v>
+        <v>11230.422</v>
       </c>
     </row>
     <row r="5">
@@ -8070,7 +8070,7 @@
         <v>783.068</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>74.38500000000001</v>
+        <v>1535.083</v>
       </c>
     </row>
     <row r="6">
@@ -8109,7 +8109,7 @@
         <v>11.862</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>18870.434</v>
+        <v>16807.94</v>
       </c>
     </row>
     <row r="9">
@@ -8135,457 +8135,496 @@
         <v>0</v>
       </c>
       <c r="C10" s="2" t="n">
+        <v>4080.378</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CostBucketOverheadsImaging</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>197.551</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CostBucketOverheads TOTAL</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2" t="n">
         <v>4277.929</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>CostBucketOverheads TOTAL</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>4277.929</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CostTypeDetailsDepreciation</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>708.082</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>329.065</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CostTypeDetailsGS</t>
+          <t>CostTypeDetailsDepreciation</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0</v>
+        <v>708.082</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>34.443</v>
+        <v>329.065</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CostTypeDetailsMS</t>
+          <t>CostTypeDetailsGS</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2316.482</v>
+        <v>0</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1013.873</v>
+        <v>34.443</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CostTypeDetailsOHC</t>
+          <t>CostTypeDetailsMS</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>356.264</v>
+        <v>2316.482</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>246.165</v>
+        <v>1013.873</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CostTypeDetailsOHDepreciation</t>
+          <t>CostTypeDetailsOHC</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0</v>
+        <v>356.264</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>80.741</v>
+        <v>246.165</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CostTypeDetailsOHF</t>
+          <t>CostTypeDetailsOHDepreciation</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>1064.346</v>
+        <v>0</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>3951.023</v>
+        <v>80.741</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CostTypeDetailsPharmacy</t>
+          <t>CostTypeDetailsOHF</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0</v>
+        <v>1064.346</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>47.125</v>
+        <v>3951.023</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CostTypeDetailsProstheses</t>
+          <t>CostTypeDetailsPharmacy</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>18233.212</v>
+        <v>47.125</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CostTypeDetailsSWAllied</t>
+          <t>CostTypeDetailsProstheses</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1422.734</v>
+        <v>0</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>931.4400000000001</v>
+        <v>18233.212</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CostTypeDetailsSWDoc</t>
+          <t>CostTypeDetailsSWAllied</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>14222.342</v>
+        <v>1422.734</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>9006.51</v>
+        <v>931.4400000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CostTypeDetailsSWNonClin</t>
+          <t>CostTypeDetailsSWDoc</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1771.391</v>
+        <v>14222.342</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0</v>
+        <v>9006.51</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>CostTypeDetailsSWNonClin</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>1771.391</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>CostTypeDetailsSWNurs</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B24" s="2" t="n">
         <v>4872.231</v>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="C24" s="2" t="n">
         <v>1530.563</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>CostTypeDetails TOTAL</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B25" s="2" t="n">
         <v>26733.872</v>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C25" s="2" t="n">
         <v>35404.16</v>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>Caries claim, no implant codes</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>1022MF4159-a9c9e9</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>codes: 02112, 33131</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Cell</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Sent</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Corrected</t>
         </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>CostBucketDirectAnaesthesia</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>75.13500000000001</v>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>10.298</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CostBucketDirectDental</t>
+          <t>CostBucketDirectAnaesthesia</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>128.363</v>
+        <v>75.13500000000001</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>389.088</v>
+        <v>23.609</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>CostBucketDirectDental</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>128.363</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>308.201</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>CostBucketDirectImaging</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n">
+      <c r="B31" s="2" t="n">
         <v>40.734</v>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>2.652</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>CostBucketDirect TOTAL</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>244.232</v>
-      </c>
       <c r="C31" s="2" t="n">
-        <v>402.038</v>
+        <v>20.237</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CostBucketOverheadsDental</t>
+          <t>CostBucketDirectProsthesis</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>161.62</v>
+        <v>49.991</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>CostBucketOverheads TOTAL</t>
+          <t>CostBucketDirect TOTAL</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0</v>
+        <v>244.232</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>161.62</v>
+        <v>402.038</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CostTypeDetailsDepreciation</t>
+          <t>CostBucketOverheadsDental</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>11.273</v>
+        <v>0</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>18.12</v>
+        <v>154.174</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CostTypeDetailsGS</t>
+          <t>CostBucketOverheadsImaging</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>1.078</v>
+        <v>7.446</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>CostTypeDetailsMS</t>
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>CostBucketOverheads TOTAL</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>13.156</v>
+        <v>0</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>40.04</v>
+        <v>161.62</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CostTypeDetailsOHC</t>
+          <t>CostTypeDetailsDepreciation</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>6.264</v>
+        <v>11.273</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>9.715999999999999</v>
+        <v>18.12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CostTypeDetailsOHDepreciation</t>
+          <t>CostTypeDetailsGS</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>2.984</v>
+        <v>1.078</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CostTypeDetailsOHF</t>
+          <t>CostTypeDetailsMS</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>17.537</v>
+        <v>13.156</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>148.92</v>
+        <v>40.04</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CostTypeDetailsPharmacy</t>
+          <t>CostTypeDetailsOHC</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>0</v>
+        <v>6.264</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>4.166</v>
+        <v>9.715999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CostTypeDetailsSWAllied</t>
+          <t>CostTypeDetailsOHDepreciation</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>16.294</v>
+        <v>0</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>7.94</v>
+        <v>2.984</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CostTypeDetailsSWDoc</t>
+          <t>CostTypeDetailsOHF</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>169.098</v>
+        <v>17.537</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>282.506</v>
+        <v>148.92</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CostTypeDetailsSWNonClin</t>
+          <t>CostTypeDetailsPharmacy</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>28.183</v>
+        <v>0</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>0</v>
+        <v>4.166</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>CostTypeDetailsSWAllied</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>16.294</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>7.94</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CostTypeDetailsSWDoc</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>169.098</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>282.506</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CostTypeDetailsSWNonClin</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>28.183</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>CostTypeDetailsSWNurs</t>
         </is>
       </c>
-      <c r="B44" s="2" t="n">
+      <c r="B47" s="2" t="n">
         <v>57.621</v>
       </c>
-      <c r="C44" s="2" t="n">
+      <c r="C47" s="2" t="n">
         <v>48.188</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
         <is>
           <t>CostTypeDetails TOTAL</t>
         </is>
       </c>
-      <c r="B45" s="2" t="n">
+      <c r="B48" s="2" t="n">
         <v>319.426</v>
       </c>
-      <c r="C45" s="2" t="n">
+      <c r="C48" s="2" t="n">
         <v>563.658</v>
       </c>
     </row>
@@ -8600,7 +8639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A262"/>
+  <dimension ref="A1:A250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -8812,1631 +8851,1547 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M01_PROD.xml: bucket Prosthesis profile SWAllied 13.0%, Prostheses 87.0%</t>
+          <t>CostSubmission_MF4159_2025_M01_PROD.xml: bucket Prosthesis profile SWNurs 3.6%, SWDoc 29.5%, SWAllied 11.1%, Prostheses 54.3%, MS 1.5%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M01_PROD.xml: bucket Dental profile SWNurs 8.2%, SWDoc 47.0%, SWAllied 2.4%, MS 7.5%, GS 0.2%, Depreciation 2.4%, OHF 29.7%, OHDepreciation 0.6%, OHC 2.0%</t>
+          <t>CostSubmission_MF4159_2025_M01_PROD.xml: bucket Dental profile SWNurs 8.1%, SWDoc 41.8%, SWAllied 2.2%, Prostheses 1.9%, MS 7.4%, GS 0.3%, Depreciation 2.6%, OHF 32.7%, OHDepreciation 0.7%, OHC 2.3%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M01_PROD.xml: bucket Anaesthesia profile SWNurs 6.5%, SWDoc 71.5%, Pharmacy 22.1%</t>
+          <t>CostSubmission_MF4159_2025_M01_PROD.xml: bucket Imaging profile SWNurs 7.4%, SWDoc 40.7%, SWAllied 4.1%, Prostheses 14.1%, MS 6.4%, Depreciation 2.1%, OHF 25.2%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M01_PROD.xml: bucket Imaging profile SWNurs 77.7%, Depreciation 22.3%</t>
+          <t>CostSubmission_MF4159_2025_M01_PROD.xml: bucket Anaesthesia profile SWNurs 9.7%, SWDoc 53.8%, Pharmacy 6.6%, Prostheses 18.6%, MS 8.4%, Depreciation 2.8%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">CostSubmission_MF4159_2025_M01_PROD.xml: bucket Laboratory profile </t>
+          <t>CostSubmission_MF4159_2025_M02_PROD.xml: claim totals -0.015 AED vs ledger absorbed by claim 760MF4159-03a04e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M02_PROD.xml: claim totals -0.015 AED vs ledger absorbed by claim 760MF4159-03a04e</t>
+          <t>CostSubmission_MF4159_2025_M02_PROD.xml: Prostheses pools abutments 4,275.00, bone_graft 9,150.00, fixtures 29,846.00, lab 15,958.44; coded claims in activity: 127</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M02_PROD.xml: Prostheses pools abutments 4,275.00, bone_graft 9,150.00, fixtures 29,846.00, lab 15,958.44; coded claims in activity: 127</t>
+          <t>CostSubmission_MF4159_2025_M02_PROD.xml: abutments pool 4,275.000 AED placed on 15 claims by units (36 units; 118.750 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M02_PROD.xml: abutments pool 4,275.000 AED placed on 15 claims by units (36 units; 118.750 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M02_PROD.xml: bone_graft pool 9,150.000 AED placed on 20 claims by units (70 units; 130.714 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M02_PROD.xml: bone_graft pool 9,150.000 AED placed on 20 claims by units (70 units; 130.714 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M02_PROD.xml: fixtures pool 29,846.000 AED placed on 15 claims by units (32 units; 932.688 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M02_PROD.xml: fixtures pool 29,846.000 AED placed on 15 claims by units (32 units; 932.688 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M02_PROD.xml: lab pool 15,958.440 AED placed on 127 claims by units (330 units; 48.359 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M02_PROD.xml: lab pool 15,958.440 AED placed on 127 claims by units (330 units; 48.359 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M02_PROD.xml: dental technicians pool 6,666.308 AED placed on 127 claims by units (330 units; 20.201 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M02_PROD.xml: dental technicians pool 6,666.308 AED placed on 127 claims by units (330 units; 20.201 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M02_PROD.xml: fils residuals {SWNurs:-19, SWDoc:+4, SWAllied:+17, Pharmacy:+36, MS:-64, GS:-23, Depreciation:+46, OHF:+17, OHDepreciation:+32, OHC:-46} absorbed by claim index 815</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M02_PROD.xml: fils residuals {SWNurs:-19, SWDoc:+4, SWAllied:+17, Pharmacy:+36, MS:-64, GS:-23, Depreciation:+46, OHF:+17, OHDepreciation:+32, OHC:-46} absorbed by claim index 815</t>
+          <t>CostSubmission_MF4159_2025_M02_PROD.xml: bucket Prosthesis profile SWNurs 3.1%, SWDoc 37.9%, SWAllied 7.9%, Prostheses 49.6%, MS 1.5%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M02_PROD.xml: bucket Prosthesis profile SWAllied 10.1%, Prostheses 89.9%</t>
+          <t>CostSubmission_MF4159_2025_M02_PROD.xml: bucket Dental profile SWNurs 6.1%, SWDoc 46.0%, SWAllied 1.7%, Prostheses 1.5%, MS 6.1%, GS 0.6%, Depreciation 2.4%, OHF 25.4%, OHDepreciation 0.6%, OHC 9.5%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M02_PROD.xml: bucket Dental profile SWNurs 6.2%, SWDoc 51.5%, SWAllied 1.8%, MS 6.2%, GS 0.5%, Depreciation 2.2%, OHF 22.9%, OHDepreciation 0.6%, OHC 8.1%</t>
+          <t>CostSubmission_MF4159_2025_M02_PROD.xml: bucket Imaging profile SWNurs 6.1%, SWDoc 49.1%, SWAllied 3.4%, Prostheses 12.1%, MS 5.8%, Depreciation 2.2%, OHF 21.4%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M02_PROD.xml: bucket Anaesthesia profile SWNurs 4.8%, SWDoc 77.5%, Pharmacy 17.7%</t>
+          <t>CostSubmission_MF4159_2025_M02_PROD.xml: bucket Anaesthesia profile SWNurs 7.7%, SWDoc 61.6%, Pharmacy 5.6%, Prostheses 15.1%, MS 7.3%, Depreciation 2.7%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M02_PROD.xml: bucket Imaging profile SWNurs 74.0%, Depreciation 26.0%</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: claim totals -0.047 AED vs ledger absorbed by claim 1776MF4159-ea919c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">CostSubmission_MF4159_2025_M02_PROD.xml: bucket Laboratory profile </t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: Prostheses pools bone_graft 7,850.00, fixtures 22,483.00, abutments 9,790.00, lab 48,028.42; coded claims in activity: 116</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: claim totals -0.047 AED vs ledger absorbed by claim 1776MF4159-ea919c</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: bone_graft pool 7,850.000 AED placed on 11 claims by units (32 units; 245.312 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: Prostheses pools bone_graft 7,850.00, fixtures 22,483.00, abutments 9,790.00, lab 48,028.42; coded claims in activity: 116</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: fixtures pool 22,483.000 AED placed on 12 claims by units (17 units; 1,322.529 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: bone_graft pool 7,850.000 AED placed on 11 claims by units (32 units; 245.312 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: abutments: claim 781MF4159-26d379 share 391.600 capped at its Dental amount 302.499</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: fixtures pool 22,483.000 AED placed on 12 claims by units (17 units; 1,322.529 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: abutments: claim 2661MF4159-d5af2d share 391.600 capped at its Dental amount 302.499</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: abutments: claim 781MF4159-26d379 share 391.600 capped at its Dental amount 302.499</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: abutments: claim 1337MF4159-ecf85b share 391.600 capped at its Dental amount 302.499</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: abutments: claim 2661MF4159-d5af2d share 391.600 capped at its Dental amount 302.499</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: abutments: claim 2669MF4159-56bb2c share 391.600 capped at its Dental amount 302.499</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: abutments: claim 1337MF4159-ecf85b share 391.600 capped at its Dental amount 302.499</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: abutments: claim 2436MF4159-aa32a4 share 391.600 capped at its Dental amount 302.499</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: abutments: claim 2669MF4159-56bb2c share 391.600 capped at its Dental amount 302.499</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: abutments: claim 1792MF4159-adecc5 share 783.200 capped at its Dental amount 635.553</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: abutments: claim 2436MF4159-aa32a4 share 391.600 capped at its Dental amount 302.499</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: abutments: claim 1941MF4159-15afa4 share 391.600 capped at its Dental amount 164.999</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: abutments: claim 1792MF4159-adecc5 share 783.200 capped at its Dental amount 635.553</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: abutments: claim 2346MF4159-af3dfb share 1,566.400 capped at its Dental amount 1,209.995</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: abutments: claim 1941MF4159-15afa4 share 391.600 capped at its Dental amount 164.999</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: abutments: claim 1790MF4159-305d29 share 391.600 capped at its Dental amount 302.499</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: abutments: claim 2346MF4159-af3dfb share 1,566.400 capped at its Dental amount 1,209.995</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: abutments pool 9,790.000 AED placed on 18 claims by units (25 units; 391.600 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: abutments: claim 1790MF4159-305d29 share 391.600 capped at its Dental amount 302.499</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 697MF4159-2ac13e share 215.374 capped at its Dental amount 201.666</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: abutments pool 9,790.000 AED placed on 18 claims by units (25 units; 391.600 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 781MF4159-26d379 share 215.374 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 697MF4159-2ac13e share 215.374 capped at its Dental amount 201.666</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 2646MF4159-7976bf share 215.374 capped at its Dental amount 201.666</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 781MF4159-26d379 share 215.374 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 615MF4159-c15e63 share 215.374 capped at its Dental amount 201.666</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 2646MF4159-7976bf share 215.374 capped at its Dental amount 201.666</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 2661MF4159-d5af2d share 215.374 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 615MF4159-c15e63 share 215.374 capped at its Dental amount 201.666</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1337MF4159-ecf85b share 215.374 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 2661MF4159-d5af2d share 215.374 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 2669MF4159-56bb2c share 215.374 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1337MF4159-ecf85b share 215.374 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1900MF4159-6f3eb9 share 215.374 capped at its Dental amount 201.666</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 2669MF4159-56bb2c share 215.374 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 2436MF4159-aa32a4 share 215.374 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1900MF4159-6f3eb9 share 215.374 capped at its Dental amount 201.666</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1736MF4159-c8f10a share 1,292.245 capped at its Dental amount 1,209.995</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 2436MF4159-aa32a4 share 215.374 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1792MF4159-adecc5 share 430.748 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1736MF4159-c8f10a share 1,292.245 capped at its Dental amount 1,209.995</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1941MF4159-15afa4 share 215.374 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1792MF4159-adecc5 share 430.748 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 2346MF4159-af3dfb share 861.497 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1941MF4159-15afa4 share 215.374 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1635MF4159-e561c4 share 1,507.619 capped at its Dental amount 1,411.661</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 2346MF4159-af3dfb share 861.497 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1978MF4159-7c60ba share 215.374 capped at its Dental amount 201.666</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1635MF4159-e561c4 share 1,507.619 capped at its Dental amount 1,411.661</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1790MF4159-305d29 share 215.374 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1978MF4159-7c60ba share 215.374 capped at its Dental amount 201.666</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1886MF4159-cb3d3f share 215.374 capped at its Dental amount 201.666</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1790MF4159-305d29 share 215.374 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1981MF4159-97470b share 215.374 capped at its Dental amount 201.666</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1886MF4159-cb3d3f share 215.374 capped at its Dental amount 201.666</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1971MF4159-abc46a share 430.748 capped at its Dental amount 403.332</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1981MF4159-97470b share 215.374 capped at its Dental amount 201.666</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1992MF4159-7be120 share 215.374 capped at its Dental amount 201.666</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1971MF4159-abc46a share 430.748 capped at its Dental amount 403.332</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab pool 48,028.420 AED placed on 107 claims by units (223 units; 215.374 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab: claim 1992MF4159-7be120 share 215.374 capped at its Dental amount 201.666</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 697MF4159-2ac13e share 32.875 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: lab pool 48,028.420 AED placed on 107 claims by units (223 units; 215.374 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 781MF4159-26d379 share 32.875 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 697MF4159-2ac13e share 32.875 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 2646MF4159-7976bf share 32.875 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 781MF4159-26d379 share 32.875 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 615MF4159-c15e63 share 32.875 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 2646MF4159-7976bf share 32.875 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 2661MF4159-d5af2d share 32.875 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 615MF4159-c15e63 share 32.875 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1337MF4159-ecf85b share 32.875 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 2661MF4159-d5af2d share 32.875 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 2669MF4159-56bb2c share 32.875 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1337MF4159-ecf85b share 32.875 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1900MF4159-6f3eb9 share 32.875 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 2669MF4159-56bb2c share 32.875 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 2436MF4159-aa32a4 share 32.875 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1900MF4159-6f3eb9 share 32.875 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1736MF4159-c8f10a share 197.248 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 2436MF4159-aa32a4 share 32.875 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1792MF4159-adecc5 share 65.749 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1736MF4159-c8f10a share 197.248 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1941MF4159-15afa4 share 32.875 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1792MF4159-adecc5 share 65.749 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 2346MF4159-af3dfb share 131.498 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1941MF4159-15afa4 share 32.875 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1635MF4159-e561c4 share 230.122 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 2346MF4159-af3dfb share 131.498 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1978MF4159-7c60ba share 32.874 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1635MF4159-e561c4 share 230.122 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1790MF4159-305d29 share 32.874 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1978MF4159-7c60ba share 32.874 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1886MF4159-cb3d3f share 32.874 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1790MF4159-305d29 share 32.874 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1981MF4159-97470b share 32.874 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1886MF4159-cb3d3f share 32.874 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1971MF4159-abc46a share 65.749 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1981MF4159-97470b share 32.874 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1992MF4159-7be120 share 32.874 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1971MF4159-abc46a share 65.749 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians pool 7,331.045 AED placed on 96 claims by units (223 units; 32.875 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians: claim 1992MF4159-7be120 share 32.874 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: fils residuals {SWNurs:-67, SWDoc:+2, SWAllied:+57, Pharmacy:+34, MS:-31, Depreciation:-25, OHF:+47, OHDepreciation:+1, OHC:-18} absorbed by claim index 180</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: dental technicians pool 7,331.045 AED placed on 96 claims by units (223 units; 32.875 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: bucket Prosthesis profile SWNurs 2.7%, SWDoc 30.2%, SWAllied 6.9%, Prostheses 58.9%, MS 1.3%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: fils residuals {SWNurs:-67, SWDoc:+2, SWAllied:+57, Pharmacy:+34, MS:-31, Depreciation:-25, OHF:+47, OHDepreciation:+1, OHC:-18} absorbed by claim index 180</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: bucket Dental profile SWNurs 5.9%, SWDoc 41.3%, SWAllied 1.7%, Prostheses 2.0%, MS 6.0%, Depreciation 2.2%, OHF 26.1%, OHDepreciation 0.6%, OHC 14.2%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: bucket Prosthesis profile SWAllied 7.7%, Prostheses 92.3%</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: bucket Imaging profile SWNurs 6.0%, SWDoc 44.5%, SWAllied 3.4%, Prostheses 16.2%, MS 5.7%, Depreciation 1.9%, OHF 22.2%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: bucket Dental profile SWNurs 6.2%, SWDoc 47.0%, SWAllied 1.8%, MS 6.2%, Depreciation 2.0%, OHF 24.0%, OHDepreciation 0.5%, OHC 12.4%</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: bucket Anaesthesia profile SWNurs 7.7%, SWDoc 56.8%, Pharmacy 5.0%, Prostheses 20.7%, MS 7.3%, Depreciation 2.5%</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: bucket Anaesthesia profile SWNurs 5.2%, SWDoc 77.7%, Pharmacy 17.1%</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: claim totals -0.004 AED vs ledger absorbed by claim 1689MF4159-a7a492</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: bucket Imaging profile SWNurs 75.5%, Depreciation 24.5%</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: Prostheses pools abutments 9,790.00, bone_graft 7,850.00, fixtures 22,483.00, lab 30,336.42; coded claims in activity: 138</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">CostSubmission_MF4159_2025_M03_PROD.xml: bucket Laboratory profile </t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: abutments: claim 1474MF4159-6abc84 share 287.941 capped at its Dental amount 256.783</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: claim totals -0.004 AED vs ledger absorbed by claim 1689MF4159-a7a492</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: abutments: claim 1580MF4159-b18ada share 287.941 capped at its Dental amount 233.225</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: Prostheses pools abutments 9,790.00, bone_graft 7,850.00, fixtures 22,483.00, lab 30,336.42; coded claims in activity: 138</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: abutments: claim 2026MF4159-47d5d0 share 575.883 capped at its Dental amount 466.449</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: abutments: claim 1474MF4159-6abc84 share 287.941 capped at its Dental amount 256.783</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: abutments: claim 388MF4159-b700c3 share 287.941 capped at its Dental amount 233.225</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: abutments: claim 1580MF4159-b18ada share 287.941 capped at its Dental amount 233.225</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: abutments pool 9,790.000 AED placed on 17 claims by units (34 units; 287.941 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: abutments: claim 2026MF4159-47d5d0 share 575.883 capped at its Dental amount 466.449</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: bone_graft pool 7,850.000 AED placed on 10 claims by units (66 units; 118.939 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: abutments: claim 388MF4159-b700c3 share 287.941 capped at its Dental amount 233.225</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: fixtures pool 22,483.000 AED placed on 10 claims by units (33 units; 681.303 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: abutments pool 9,790.000 AED placed on 17 claims by units (34 units; 287.941 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: lab: claim 1474MF4159-6abc84 share 86.183 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: bone_graft pool 7,850.000 AED placed on 10 claims by units (66 units; 118.939 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: lab: claim 1580MF4159-b18ada share 86.183 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: fixtures pool 22,483.000 AED placed on 10 claims by units (33 units; 681.303 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: lab: claim 2026MF4159-47d5d0 share 172.366 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: lab: claim 1474MF4159-6abc84 share 86.183 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: lab: claim 388MF4159-b700c3 share 86.183 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: lab: claim 1580MF4159-b18ada share 86.183 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: lab pool 30,336.420 AED placed on 134 claims by units (352 units; 86.183 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: lab: claim 2026MF4159-47d5d0 share 172.366 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: dental technicians: claim 1474MF4159-6abc84 share 11.957 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: lab: claim 388MF4159-b700c3 share 86.183 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: dental technicians: claim 1580MF4159-b18ada share 11.957 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: lab pool 30,336.420 AED placed on 134 claims by units (352 units; 86.183 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: dental technicians: claim 2026MF4159-47d5d0 share 23.914 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: dental technicians: claim 1474MF4159-6abc84 share 11.957 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: dental technicians: claim 388MF4159-b700c3 share 11.957 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: dental technicians: claim 1580MF4159-b18ada share 11.957 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: dental technicians pool 4,208.914 AED placed on 134 claims by units (352 units; 11.957 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: dental technicians: claim 2026MF4159-47d5d0 share 23.914 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: fils residuals {SWNurs:-32, SWDoc:-50, SWAllied:-21, Pharmacy:+2, MS:+32, GS:+27, Depreciation:-1, OHF:+47, OHDepreciation:+30, OHC:-34} absorbed by claim index 243</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: dental technicians: claim 388MF4159-b700c3 share 11.957 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: bucket Prosthesis profile SWNurs 3.7%, SWDoc 27.0%, SWAllied 5.6%, Prostheses 62.0%, MS 1.7%</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: dental technicians pool 4,208.914 AED placed on 134 claims by units (352 units; 11.957 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: bucket Dental profile SWNurs 7.0%, SWDoc 31.7%, SWAllied 1.9%, Prostheses 1.8%, MS 6.8%, GS 0.2%, Depreciation 2.4%, OHF 30.4%, OHDepreciation 0.7%, OHC 17.1%</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: fils residuals {SWNurs:-32, SWDoc:-50, SWAllied:-21, Pharmacy:+2, MS:+32, GS:+27, Depreciation:-1, OHF:+47, OHDepreciation:+30, OHC:-34} absorbed by claim index 243</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: bucket Imaging profile SWNurs 7.5%, SWDoc 36.2%, SWAllied 4.0%, Prostheses 15.6%, MS 6.9%, Depreciation 2.3%, OHF 27.5%</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: bucket Prosthesis profile SWAllied 5.6%, Prostheses 94.4%</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: bucket Anaesthesia profile SWNurs 10.3%, SWDoc 49.5%, Pharmacy 6.4%, Prostheses 21.3%, MS 9.4%, Depreciation 3.2%</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: bucket Dental profile SWNurs 7.4%, SWDoc 36.7%, SWAllied 2.1%, MS 7.1%, GS 0.2%, Depreciation 2.3%, OHF 28.5%, OHDepreciation 0.6%, OHC 15.2%</t>
+          <t>CostSubmission_MF4159_2025_M05_PROD.xml: claim totals -0.037 AED vs ledger absorbed by claim 1351MF4159-60207a</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: bucket Anaesthesia profile SWNurs 7.3%, SWDoc 70.0%, Pharmacy 22.7%</t>
+          <t>CostSubmission_MF4159_2025_M05_PROD.xml: Prostheses pools bone_graft 8,935.00, fixtures 32,196.97, abutments 1,340.00, lab 21,167.08; coded claims in activity: 140</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: bucket Imaging profile SWNurs 76.3%, Depreciation 23.7%</t>
+          <t>CostSubmission_MF4159_2025_M05_PROD.xml: bone_graft pool 8,935.000 AED placed on 20 claims by units (72 units; 124.097 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">CostSubmission_MF4159_2025_M04_PROD.xml: bucket Laboratory profile </t>
+          <t>CostSubmission_MF4159_2025_M05_PROD.xml: fixtures pool 32,196.970 AED placed on 19 claims by units (38 units; 847.289 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M05_PROD.xml: claim totals -0.037 AED vs ledger absorbed by claim 1351MF4159-60207a</t>
+          <t>CostSubmission_MF4159_2025_M05_PROD.xml: abutments pool 1,340.000 AED placed on 21 claims by units (35 units; 38.286 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M05_PROD.xml: Prostheses pools bone_graft 8,935.00, fixtures 32,196.97, abutments 1,340.00, lab 21,167.08; coded claims in activity: 140</t>
+          <t>CostSubmission_MF4159_2025_M05_PROD.xml: lab pool 21,167.080 AED placed on 140 claims by units (319 units; 66.354 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M05_PROD.xml: bone_graft pool 8,935.000 AED placed on 20 claims by units (72 units; 124.097 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M05_PROD.xml: dental technicians pool 7,160.511 AED placed on 140 claims by units (319 units; 22.447 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M05_PROD.xml: fixtures pool 32,196.970 AED placed on 19 claims by units (38 units; 847.289 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M05_PROD.xml: fils residuals {SWNurs:-42, SWDoc:+8, SWAllied:-65, Pharmacy:-67, MS:+29, Depreciation:-20, OHF:+137, OHDepreciation:+65, OHC:-45} absorbed by claim index 54</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M05_PROD.xml: abutments pool 1,340.000 AED placed on 21 claims by units (35 units; 38.286 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M05_PROD.xml: bucket Prosthesis profile SWNurs 4.4%, SWDoc 30.8%, SWAllied 8.8%, Prostheses 54.7%, MS 1.3%</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M05_PROD.xml: lab pool 21,167.080 AED placed on 140 claims by units (319 units; 66.354 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M05_PROD.xml: bucket Dental profile SWNurs 9.2%, SWDoc 40.6%, SWAllied 2.3%, Prostheses 1.8%, MS 5.8%, Depreciation 2.7%, OHF 36.3%, OHDepreciation 0.7%, OHC 0.7%</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M05_PROD.xml: dental technicians pool 7,160.511 AED placed on 140 claims by units (319 units; 22.447 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M05_PROD.xml: bucket Imaging profile SWNurs 8.3%, SWDoc 39.4%, SWAllied 4.1%, Prostheses 13.1%, MS 5.0%, Depreciation 2.2%, OHF 27.8%</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M05_PROD.xml: fils residuals {SWNurs:-42, SWDoc:+8, SWAllied:-65, Pharmacy:-67, MS:+29, Depreciation:-20, OHF:+137, OHDepreciation:+65, OHC:-45} absorbed by claim index 54</t>
+          <t>CostSubmission_MF4159_2025_M05_PROD.xml: bucket Anaesthesia profile SWNurs 11.5%, SWDoc 54.2%, Pharmacy 6.5%, Prostheses 18.0%, MS 6.8%, Depreciation 3.0%</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M05_PROD.xml: bucket Prosthesis profile SWAllied 10.1%, Prostheses 89.9%</t>
+          <t>CostSubmission_MF4159_2025_M06_PROD.xml: claim totals +0.022 AED vs ledger absorbed by claim 165MF4159-98360e</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M05_PROD.xml: bucket Dental profile SWNurs 9.4%, SWDoc 45.7%, SWAllied 2.4%, MS 5.9%, Depreciation 2.5%, OHF 32.9%, OHDepreciation 0.6%, OHC 0.6%</t>
+          <t>CostSubmission_MF4159_2025_M06_PROD.xml: Prostheses pools fixtures 30,303.03, bone_graft 8,512.50, abutments 1,750.00, lab 12,441.50; coded claims in activity: 120</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M05_PROD.xml: bucket Anaesthesia profile SWNurs 7.5%, SWDoc 71.1%, Pharmacy 21.4%</t>
+          <t>CostSubmission_MF4159_2025_M06_PROD.xml: fixtures pool 30,303.030 AED placed on 15 claims by units (34 units; 891.266 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M05_PROD.xml: bucket Imaging profile SWNurs 79.3%, Depreciation 20.7%</t>
+          <t>CostSubmission_MF4159_2025_M06_PROD.xml: bone_graft pool 8,512.500 AED placed on 15 claims by units (66 units; 128.977 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">CostSubmission_MF4159_2025_M05_PROD.xml: bucket Laboratory profile </t>
+          <t>CostSubmission_MF4159_2025_M06_PROD.xml: abutments pool 1,750.000 AED placed on 23 claims by units (33 units; 53.030 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M06_PROD.xml: claim totals +0.022 AED vs ledger absorbed by claim 165MF4159-98360e</t>
+          <t>CostSubmission_MF4159_2025_M06_PROD.xml: lab pool 12,441.500 AED placed on 120 claims by units (280 units; 44.434 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M06_PROD.xml: Prostheses pools fixtures 30,303.03, bone_graft 8,512.50, abutments 1,750.00, lab 12,441.50; coded claims in activity: 120</t>
+          <t>CostSubmission_MF4159_2025_M06_PROD.xml: fils residuals {SWNurs:+67, SWDoc:-59, SWAllied:+15, Pharmacy:-48, MS:+17, Depreciation:+41, OHF:+16, OHDepreciation:-64, OHC:+15} absorbed by claim index 419</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M06_PROD.xml: fixtures pool 30,303.030 AED placed on 15 claims by units (34 units; 891.266 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M06_PROD.xml: bucket Prosthesis profile SWNurs 6.9%, SWDoc 40.6%, SWAllied 1.7%, Prostheses 49.4%, MS 1.3%</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M06_PROD.xml: bone_graft pool 8,512.500 AED placed on 15 claims by units (66 units; 128.977 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M06_PROD.xml: bucket Dental profile SWNurs 9.8%, SWDoc 36.2%, SWAllied 2.5%, Prostheses 1.1%, MS 4.1%, Depreciation 2.0%, OHF 36.0%, OHDepreciation 0.5%, OHC 7.8%</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M06_PROD.xml: abutments pool 1,750.000 AED placed on 23 claims by units (33 units; 53.030 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M06_PROD.xml: bucket Imaging profile SWNurs 10.0%, SWDoc 39.4%, SWAllied 5.0%, Prostheses 9.0%, MS 3.9%, Depreciation 1.8%, OHF 30.9%</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M06_PROD.xml: lab pool 12,441.500 AED placed on 120 claims by units (280 units; 44.434 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M06_PROD.xml: bucket Anaesthesia profile SWNurs 14.9%, SWDoc 58.3%, Pharmacy 5.1%, Prostheses 13.3%, MS 5.8%, Depreciation 2.6%</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M06_PROD.xml: fils residuals {SWNurs:+67, SWDoc:-59, SWAllied:+15, Pharmacy:-48, MS:+17, Depreciation:+41, OHF:+16, OHDepreciation:-64, OHC:+15} absorbed by claim index 419</t>
+          <t>CostSubmission_MF4159_2025_M07_PROD.xml: claim totals -0.020 AED vs ledger absorbed by claim 2066MF4159-ff09af</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M06_PROD.xml: bucket Prosthesis profile Prostheses 100.0%</t>
+          <t>CostSubmission_MF4159_2025_M07_PROD.xml: Prostheses pools fixtures 14,810.61, abutments 6,350.00, bone_graft 5,800.00, lab 19,563.99; coded claims in activity: 122</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M06_PROD.xml: bucket Dental profile SWNurs 10.1%, SWDoc 41.1%, SWAllied 2.7%, MS 4.2%, Depreciation 1.8%, OHF 32.9%, OHDepreciation 0.5%, OHC 6.7%</t>
+          <t>CostSubmission_MF4159_2025_M07_PROD.xml: fixtures pool 14,810.610 AED placed on 9 claims by units (19 units; 779.506 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M06_PROD.xml: bucket Anaesthesia profile SWNurs 9.5%, SWDoc 74.3%, Pharmacy 16.2%</t>
+          <t>CostSubmission_MF4159_2025_M07_PROD.xml: abutments pool 6,350.000 AED placed on 16 claims by units (32 units; 198.438 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M06_PROD.xml: bucket Imaging profile SWNurs 84.9%, Depreciation 15.1%</t>
+          <t>CostSubmission_MF4159_2025_M07_PROD.xml: bone_graft pool 5,800.000 AED placed on 8 claims by units (35 units; 165.714 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">CostSubmission_MF4159_2025_M06_PROD.xml: bucket Laboratory profile </t>
+          <t>CostSubmission_MF4159_2025_M07_PROD.xml: lab: claim 1719MF4159-6bb02a share 223.163 capped at its Dental amount 130.282</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M07_PROD.xml: claim totals -0.020 AED vs ledger absorbed by claim 2066MF4159-ff09af</t>
+          <t>CostSubmission_MF4159_2025_M07_PROD.xml: lab: claim 1936MF4159-00e706 share 148.776 capped at its Dental amount 86.855</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M07_PROD.xml: Prostheses pools fixtures 14,810.61, abutments 6,350.00, bone_graft 5,800.00, lab 19,563.99; coded claims in activity: 122</t>
+          <t>CostSubmission_MF4159_2025_M07_PROD.xml: lab: claim 2158MF4159-35df2b share 74.388 capped at its Dental amount 43.428</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M07_PROD.xml: fixtures pool 14,810.610 AED placed on 9 claims by units (19 units; 779.506 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M07_PROD.xml: lab pool 19,563.990 AED placed on 122 claims by units (263 units; 74.388 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M07_PROD.xml: abutments pool 6,350.000 AED placed on 16 claims by units (32 units; 198.438 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M07_PROD.xml: dental technicians: claim 1719MF4159-6bb02a share 71.804 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M07_PROD.xml: bone_graft pool 5,800.000 AED placed on 8 claims by units (35 units; 165.714 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M07_PROD.xml: dental technicians: claim 1936MF4159-00e706 share 47.869 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M07_PROD.xml: lab: claim 1719MF4159-6bb02a share 223.163 capped at its Dental amount 130.282</t>
+          <t>CostSubmission_MF4159_2025_M07_PROD.xml: dental technicians: claim 2158MF4159-35df2b share 23.934 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M07_PROD.xml: lab: claim 1936MF4159-00e706 share 148.776 capped at its Dental amount 86.855</t>
+          <t>CostSubmission_MF4159_2025_M07_PROD.xml: dental technicians pool 6,294.796 AED placed on 119 claims by units (263 units; 23.935 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M07_PROD.xml: lab: claim 2158MF4159-35df2b share 74.388 capped at its Dental amount 43.428</t>
+          <t>CostSubmission_MF4159_2025_M07_PROD.xml: fils residuals {SWNurs:+56, SWDoc:-63, SWAllied:+71, Pharmacy:+9, MS:-61, Depreciation:-54, OHF:+39, OHDepreciation:-29, OHC:+32} absorbed by claim index 362</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M07_PROD.xml: lab pool 19,563.990 AED placed on 122 claims by units (263 units; 74.388 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M07_PROD.xml: bucket Prosthesis profile SWNurs 5.8%, SWDoc 33.0%, SWAllied 10.0%, Prostheses 49.5%, MS 1.7%</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M07_PROD.xml: dental technicians: claim 1719MF4159-6bb02a share 71.804 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M07_PROD.xml: bucket Dental profile SWNurs 9.5%, SWDoc 33.9%, SWAllied 2.6%, Prostheses 1.3%, MS 6.0%, Depreciation 2.6%, OHF 36.5%, OHDepreciation 0.7%, OHC 6.8%</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M07_PROD.xml: dental technicians: claim 1936MF4159-00e706 share 47.869 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M07_PROD.xml: bucket Imaging profile SWNurs 9.5%, SWDoc 36.2%, SWAllied 5.2%, Prostheses 10.2%, MS 5.7%, Depreciation 2.3%, OHF 30.8%</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M07_PROD.xml: dental technicians: claim 2158MF4159-35df2b share 23.934 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M07_PROD.xml: bucket Anaesthesia profile SWNurs 13.5%, SWDoc 51.4%, Pharmacy 9.3%, Prostheses 14.4%, MS 8.1%, Depreciation 3.3%</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M07_PROD.xml: dental technicians pool 6,294.796 AED placed on 119 claims by units (263 units; 23.935 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: claim totals -0.040 AED vs ledger absorbed by claim 1749MF4159-288273</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M07_PROD.xml: fils residuals {SWNurs:+56, SWDoc:-63, SWAllied:+71, Pharmacy:+9, MS:-61, Depreciation:-54, OHF:+39, OHDepreciation:-29, OHC:+32} absorbed by claim index 362</t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: Prostheses pools fixtures 24,948.24, bone_graft 4,150.00, abutments 4,900.00, lab 35,990.74; coded claims in activity: 128</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M07_PROD.xml: bucket Prosthesis profile SWAllied 11.9%, Prostheses 88.1%</t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: fixtures pool 24,948.240 AED placed on 11 claims by units (34 units; 733.772 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M07_PROD.xml: bucket Dental profile SWNurs 9.8%, SWDoc 38.6%, SWAllied 2.8%, MS 6.2%, Depreciation 2.4%, OHF 33.5%, OHDepreciation 0.6%, OHC 6.0%</t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: bone_graft pool 4,150.000 AED placed on 8 claims by units (45 units; 92.222 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M07_PROD.xml: bucket Anaesthesia profile SWNurs 8.3%, SWDoc 63.0%, Pharmacy 28.7%</t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: abutments pool 4,900.000 AED placed on 24 claims by units (52 units; 94.231 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M07_PROD.xml: bucket Imaging profile SWNurs 80.5%, Depreciation 19.5%</t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: lab: claim 2024MF4159-87c40f share 92.521 capped at its Dental amount 27.225</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">CostSubmission_MF4159_2025_M07_PROD.xml: bucket Laboratory profile </t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: lab pool 35,990.740 AED placed on 128 claims by units (389 units; 92.521 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: claim totals -0.040 AED vs ledger absorbed by claim 1749MF4159-288273</t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: dental technicians: claim 2024MF4159-87c40f share 32.893 capped at its Dental amount 0.000</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: Prostheses pools fixtures 24,948.24, bone_graft 4,150.00, abutments 4,900.00, lab 35,990.74; coded claims in activity: 128</t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: dental technicians: claim 2145MF4159-7f25c0 share 32.892 capped at its Dental amount 22.873</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: fixtures pool 24,948.240 AED placed on 11 claims by units (34 units; 733.772 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: dental technicians: claim 2179MF4159-92f1be share 65.785 capped at its Dental amount 45.746</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: bone_graft pool 4,150.000 AED placed on 8 claims by units (45 units; 92.222 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: dental technicians: claim 1789MF4159-5c32d1 share 32.892 capped at its Dental amount 22.873</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: abutments pool 4,900.000 AED placed on 24 claims by units (52 units; 94.231 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: dental technicians: claim 1745MF4159-7deac0 share 98.677 capped at its Dental amount 68.619</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: lab: claim 2024MF4159-87c40f share 92.521 capped at its Dental amount 27.225</t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: dental technicians: claim 389MF4159-ea32e5 share 32.892 capped at its Dental amount 22.873</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: lab pool 35,990.740 AED placed on 128 claims by units (389 units; 92.521 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: dental technicians: claim 391MF4159-5cbd8c share 32.892 capped at its Dental amount 22.874</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: dental technicians: claim 2024MF4159-87c40f share 32.893 capped at its Dental amount 0.000</t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: dental technicians pool 12,795.132 AED placed on 127 claims by units (389 units; 32.892 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: dental technicians: claim 2145MF4159-7f25c0 share 32.892 capped at its Dental amount 22.873</t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: fils residuals {SWNurs:-84, SWDoc:-14, SWAllied:+57, Pharmacy:+44, MS:+11, Depreciation:+16, OHF:-17, OHDepreciation:+40, OHC:-53} absorbed by claim index 157</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: dental technicians: claim 2179MF4159-92f1be share 65.785 capped at its Dental amount 45.746</t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: bucket Prosthesis profile SWNurs 4.8%, SWDoc 23.5%, SWAllied 14.0%, Prostheses 56.2%, MS 1.5%</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: dental technicians: claim 1789MF4159-5c32d1 share 32.892 capped at its Dental amount 22.873</t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: bucket Dental profile SWNurs 9.9%, SWDoc 30.3%, SWAllied 2.4%, Prostheses 1.8%, MS 6.7%, Depreciation 2.5%, OHF 38.7%, OHDepreciation 0.7%, OHC 7.1%</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: dental technicians: claim 1745MF4159-7deac0 share 98.677 capped at its Dental amount 68.619</t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: bucket Imaging profile SWNurs 9.6%, SWDoc 31.5%, SWAllied 4.6%, Prostheses 14.2%, MS 6.1%, Depreciation 2.1%, OHF 31.8%</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: dental technicians: claim 389MF4159-ea32e5 share 32.892 capped at its Dental amount 22.873</t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: bucket Anaesthesia profile SWNurs 13.9%, SWDoc 45.6%, Pharmacy 8.0%, Prostheses 20.5%, MS 8.9%, Depreciation 3.1%</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: dental technicians: claim 391MF4159-5cbd8c share 32.892 capped at its Dental amount 22.874</t>
+          <t>CostSubmission_MF4159_2025_M09_PROD.xml: claim totals -0.038 AED vs ledger absorbed by claim 1478MF4159-4ccb54</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: dental technicians pool 12,795.132 AED placed on 127 claims by units (389 units; 32.892 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M09_PROD.xml: Prostheses pools abutments 2,500.00, fixtures 29,426.15, bone_graft 9,400.00, lab 16,276.17; coded claims in activity: 110</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: fils residuals {SWNurs:-84, SWDoc:-14, SWAllied:+57, Pharmacy:+44, MS:+11, Depreciation:+16, OHF:-17, OHDepreciation:+40, OHC:-53} absorbed by claim index 157</t>
+          <t>CostSubmission_MF4159_2025_M09_PROD.xml: abutments pool 2,500.000 AED placed on 21 claims by units (42 units; 59.524 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: bucket Prosthesis profile SWAllied 15.5%, Prostheses 84.5%</t>
+          <t>CostSubmission_MF4159_2025_M09_PROD.xml: fixtures pool 29,426.150 AED placed on 13 claims by units (31 units; 949.231 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: bucket Dental profile SWNurs 10.3%, SWDoc 35.0%, SWAllied 2.6%, MS 6.9%, Depreciation 2.3%, OHF 36.0%, OHDepreciation 0.6%, OHC 6.3%</t>
+          <t>CostSubmission_MF4159_2025_M09_PROD.xml: bone_graft pool 9,400.000 AED placed on 15 claims by units (67 units; 140.299 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: bucket Anaesthesia profile SWNurs 9.6%, SWDoc 62.9%, Pharmacy 27.4%</t>
+          <t>CostSubmission_MF4159_2025_M09_PROD.xml: lab pool 16,276.170 AED placed on 110 claims by units (327 units; 49.774 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: bucket Imaging profile SWNurs 81.8%, Depreciation 18.2%</t>
+          <t>CostSubmission_MF4159_2025_M09_PROD.xml: dental technicians pool 10,676.482 AED placed on 110 claims by units (327 units; 32.650 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t xml:space="preserve">CostSubmission_MF4159_2025_M08_PROD.xml: bucket Laboratory profile </t>
+          <t>CostSubmission_MF4159_2025_M09_PROD.xml: fils residuals {SWNurs:+9, SWDoc:-16, SWAllied:+25, Pharmacy:-3, MS:+13, Depreciation:+39, OHF:-39, OHDepreciation:-50, OHC:+22} absorbed by claim index 18</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M09_PROD.xml: claim totals -0.038 AED vs ledger absorbed by claim 1478MF4159-4ccb54</t>
+          <t>CostSubmission_MF4159_2025_M09_PROD.xml: bucket Prosthesis profile SWNurs 3.5%, SWDoc 29.3%, SWAllied 13.4%, Prostheses 52.3%, MS 1.4%</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M09_PROD.xml: Prostheses pools abutments 2,500.00, fixtures 29,426.15, bone_graft 9,400.00, lab 16,276.17; coded claims in activity: 110</t>
+          <t>CostSubmission_MF4159_2025_M09_PROD.xml: bucket Dental profile SWNurs 6.5%, SWDoc 33.9%, SWAllied 2.4%, Prostheses 1.5%, MS 5.6%, Depreciation 2.5%, OHF 39.5%, OHDepreciation 0.7%, OHC 7.4%</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M09_PROD.xml: abutments pool 2,500.000 AED placed on 21 claims by units (42 units; 59.524 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M09_PROD.xml: bucket Imaging profile SWNurs 6.5%, SWDoc 36.1%, SWAllied 4.8%, Prostheses 12.1%, MS 5.3%, Depreciation 2.2%, OHF 33.1%</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M09_PROD.xml: fixtures pool 29,426.150 AED placed on 13 claims by units (31 units; 949.231 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M09_PROD.xml: bucket Anaesthesia profile SWNurs 9.1%, SWDoc 50.4%, Pharmacy 13.1%, Prostheses 16.9%, MS 7.4%, Depreciation 3.1%</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M09_PROD.xml: bone_graft pool 9,400.000 AED placed on 15 claims by units (67 units; 140.299 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M10_PROD.xml: claim totals -0.084 AED vs ledger absorbed by claim 2140MF4159-5323ad</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M09_PROD.xml: lab pool 16,276.170 AED placed on 110 claims by units (327 units; 49.774 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M10_PROD.xml: Prostheses pools abutments 3,755.00, fixtures 18,497.17, bone_graft 10,880.00, lab 16,393.19; coded claims in activity: 123</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M09_PROD.xml: dental technicians pool 10,676.482 AED placed on 110 claims by units (327 units; 32.650 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M10_PROD.xml: abutments pool 3,755.000 AED placed on 22 claims by units (36 units; 104.306 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M09_PROD.xml: fils residuals {SWNurs:+9, SWDoc:-16, SWAllied:+25, Pharmacy:-3, MS:+13, Depreciation:+39, OHF:-39, OHDepreciation:-50, OHC:+22} absorbed by claim index 18</t>
+          <t>CostSubmission_MF4159_2025_M10_PROD.xml: fixtures pool 18,497.170 AED placed on 13 claims by units (29 units; 637.833 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M09_PROD.xml: bucket Prosthesis profile SWAllied 15.6%, Prostheses 84.4%</t>
+          <t>CostSubmission_MF4159_2025_M10_PROD.xml: bone_graft pool 10,880.000 AED placed on 11 claims by units (50 units; 217.600 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M09_PROD.xml: bucket Dental profile SWNurs 6.8%, SWDoc 38.9%, SWAllied 2.6%, MS 5.8%, Depreciation 2.3%, OHF 36.5%, OHDepreciation 0.6%, OHC 6.5%</t>
+          <t>CostSubmission_MF4159_2025_M10_PROD.xml: lab pool 16,393.190 AED placed on 123 claims by units (276 units; 59.396 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M09_PROD.xml: bucket Anaesthesia profile SWNurs 5.2%, SWDoc 57.4%, Pharmacy 37.4%</t>
+          <t>CostSubmission_MF4159_2025_M10_PROD.xml: dental technicians pool 7,091.542 AED placed on 123 claims by units (276 units; 25.694 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M09_PROD.xml: bucket Imaging profile SWNurs 74.6%, Depreciation 25.4%</t>
+          <t>CostSubmission_MF4159_2025_M10_PROD.xml: fils residuals {SWNurs:+42, SWDoc:+4, SWAllied:-6, Pharmacy:-33, MS:+49, GS:-1, Depreciation:-25, OHF:+24, OHDepreciation:-43, OHC:-11} absorbed by claim index 492</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t xml:space="preserve">CostSubmission_MF4159_2025_M09_PROD.xml: bucket Laboratory profile </t>
+          <t>CostSubmission_MF4159_2025_M10_PROD.xml: bucket Prosthesis profile SWNurs 4.8%, SWDoc 38.3%, SWAllied 9.5%, Prostheses 45.9%, MS 1.4%</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M10_PROD.xml: claim totals -0.084 AED vs ledger absorbed by claim 2140MF4159-5323ad</t>
+          <t>CostSubmission_MF4159_2025_M10_PROD.xml: bucket Dental profile SWNurs 8.0%, SWDoc 39.7%, SWAllied 2.1%, Prostheses 1.2%, MS 5.1%, GS 0.3%, Depreciation 2.3%, OHF 34.5%, OHDepreciation 0.6%, OHC 6.1%</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M10_PROD.xml: Prostheses pools abutments 3,755.00, fixtures 18,497.17, bone_graft 10,880.00, lab 16,393.19; coded claims in activity: 123</t>
+          <t>CostSubmission_MF4159_2025_M10_PROD.xml: bucket Imaging profile SWNurs 8.0%, SWDoc 42.3%, SWAllied 4.2%, Prostheses 9.5%, MS 4.8%, Depreciation 2.0%, OHF 29.1%</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M10_PROD.xml: abutments pool 3,755.000 AED placed on 22 claims by units (36 units; 104.306 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M10_PROD.xml: bucket Anaesthesia profile SWNurs 11.2%, SWDoc 59.6%, Pharmacy 6.2%, Prostheses 13.4%, MS 6.8%, Depreciation 2.9%</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M10_PROD.xml: fixtures pool 18,497.170 AED placed on 13 claims by units (29 units; 637.833 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M11_PROD.xml: claim totals -0.041 AED vs ledger absorbed by claim 1738MF4159-0b278e</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M10_PROD.xml: bone_graft pool 10,880.000 AED placed on 11 claims by units (50 units; 217.600 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M11_PROD.xml: Prostheses pools abutments 2,745.00, fixtures 9,022.73, bone_graft 6,225.00, lab 35,933.97; coded claims in activity: 107</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M10_PROD.xml: lab pool 16,393.190 AED placed on 123 claims by units (276 units; 59.396 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M11_PROD.xml: abutments pool 2,745.000 AED placed on 20 claims by units (40 units; 68.625 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M10_PROD.xml: dental technicians pool 7,091.542 AED placed on 123 claims by units (276 units; 25.694 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M11_PROD.xml: fixtures pool 9,022.730 AED placed on 10 claims by units (17 units; 530.749 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M10_PROD.xml: fils residuals {SWNurs:+42, SWDoc:+4, SWAllied:-6, Pharmacy:-33, MS:+49, GS:-1, Depreciation:-25, OHF:+24, OHDepreciation:-43, OHC:-11} absorbed by claim index 492</t>
+          <t>CostSubmission_MF4159_2025_M11_PROD.xml: bone_graft pool 6,225.000 AED placed on 13 claims by units (30 units; 207.500 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M10_PROD.xml: bucket Prosthesis profile SWAllied 12.5%, Prostheses 87.5%</t>
+          <t>CostSubmission_MF4159_2025_M11_PROD.xml: lab pool 35,933.970 AED placed on 107 claims by units (249 units; 144.313 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M10_PROD.xml: bucket Dental profile SWNurs 8.2%, SWDoc 44.8%, SWAllied 2.3%, MS 5.2%, GS 0.3%, Depreciation 2.1%, OHF 31.4%, OHDepreciation 0.5%, OHC 5.3%</t>
+          <t>CostSubmission_MF4159_2025_M11_PROD.xml: dental technicians pool 10,339.683 AED placed on 107 claims by units (249 units; 41.525 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M10_PROD.xml: bucket Anaesthesia profile SWNurs 7.0%, SWDoc 73.8%, Pharmacy 19.2%</t>
+          <t>CostSubmission_MF4159_2025_M11_PROD.xml: fils residuals {SWNurs:+28, SWDoc:+18, SWAllied:-8, Pharmacy:+23, MS:-10, Depreciation:-92, OHF:+46, OHDepreciation:+49, OHC:-54} absorbed by claim index 81</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M10_PROD.xml: bucket Imaging profile SWNurs 79.7%, Depreciation 20.3%</t>
+          <t>CostSubmission_MF4159_2025_M11_PROD.xml: bucket Prosthesis profile SWNurs 4.7%, SWDoc 28.5%, SWAllied 13.6%, Prostheses 51.7%, MS 1.5%</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t xml:space="preserve">CostSubmission_MF4159_2025_M10_PROD.xml: bucket Laboratory profile </t>
+          <t>CostSubmission_MF4159_2025_M11_PROD.xml: bucket Dental profile SWNurs 8.4%, SWDoc 32.0%, SWAllied 2.2%, Prostheses 1.5%, MS 5.7%, Depreciation 2.6%, OHF 40.3%, OHDepreciation 0.7%, OHC 6.7%</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M11_PROD.xml: claim totals -0.041 AED vs ledger absorbed by claim 1738MF4159-0b278e</t>
+          <t>CostSubmission_MF4159_2025_M11_PROD.xml: bucket Imaging profile SWNurs 8.4%, SWDoc 34.2%, SWAllied 4.3%, Prostheses 11.6%, MS 5.4%, Depreciation 2.3%, OHF 33.9%</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M11_PROD.xml: Prostheses pools abutments 2,745.00, fixtures 9,022.73, bone_graft 6,225.00, lab 35,933.97; coded claims in activity: 107</t>
+          <t>CostSubmission_MF4159_2025_M11_PROD.xml: bucket Anaesthesia profile SWNurs 12.5%, SWDoc 51.0%, Pharmacy 7.7%, Prostheses 17.3%, MS 8.1%, Depreciation 3.4%</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M11_PROD.xml: abutments pool 2,745.000 AED placed on 20 claims by units (40 units; 68.625 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: claim totals +0.061 AED vs ledger absorbed by claim 2043MF4159-174974</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M11_PROD.xml: fixtures pool 9,022.730 AED placed on 10 claims by units (17 units; 530.749 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: Prostheses pools abutments 1,850.00, fixtures 16,598.48, bone_graft 9,450.00, lab 41,042.50; coded claims in activity: 115</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M11_PROD.xml: bone_graft pool 6,225.000 AED placed on 13 claims by units (30 units; 207.500 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: abutments pool 1,850.000 AED placed on 20 claims by units (37 units; 50.000 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M11_PROD.xml: lab pool 35,933.970 AED placed on 107 claims by units (249 units; 144.313 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: fixtures pool 16,598.480 AED placed on 10 claims by units (15 units; 1,106.565 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M11_PROD.xml: dental technicians pool 10,339.683 AED placed on 107 claims by units (249 units; 41.525 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: bone_graft pool 9,450.000 AED placed on 8 claims by units (26 units; 363.462 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M11_PROD.xml: fils residuals {SWNurs:+28, SWDoc:+18, SWAllied:-8, Pharmacy:+23, MS:-10, Depreciation:-92, OHF:+46, OHDepreciation:+49, OHC:-54} absorbed by claim index 81</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: lab pool 41,042.500 AED placed on 115 claims by units (259 units; 158.465 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M11_PROD.xml: bucket Prosthesis profile SWAllied 16.1%, Prostheses 83.9%</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians: claim 2073MF4159-5b1531 share 75.348 capped at its Dental amount 56.779</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M11_PROD.xml: bucket Dental profile SWNurs 8.7%, SWDoc 36.8%, SWAllied 2.4%, MS 5.9%, Depreciation 2.4%, OHF 37.2%, OHDepreciation 0.6%, OHC 5.9%</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians: claim 2095MF4159-4d3bdb share 75.348 capped at its Dental amount 56.779</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M11_PROD.xml: bucket Anaesthesia profile SWNurs 8.1%, SWDoc 66.6%, Pharmacy 25.2%</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians: claim 2123MF4159-237d2d share 75.348 capped at its Dental amount 56.779</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M11_PROD.xml: bucket Imaging profile SWNurs 78.6%, Depreciation 21.4%</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians: claim 2128MF4159-e95eeb share 75.348 capped at its Dental amount 56.779</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t xml:space="preserve">CostSubmission_MF4159_2025_M11_PROD.xml: bucket Laboratory profile </t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians: claim 2135MF4159-8747a5 share 150.696 capped at its Dental amount 113.557</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: claim totals +0.061 AED vs ledger absorbed by claim 2043MF4159-174974</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians: claim 2175MF4159-57b801 share 75.348 capped at its Dental amount 56.779</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: Prostheses pools abutments 1,850.00, fixtures 16,598.48, bone_graft 9,450.00, lab 41,042.50; coded claims in activity: 115</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians: claim 2197MF4159-9b3fae share 75.348 capped at its Dental amount 56.779</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: abutments pool 1,850.000 AED placed on 20 claims by units (37 units; 50.000 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians: claim 2212MF4159-1be1ce share 904.174 capped at its Dental amount 788.968</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: fixtures pool 16,598.480 AED placed on 10 claims by units (15 units; 1,106.565 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians: claim 2245MF4159-c3ee38 share 75.348 capped at its Dental amount 56.779</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: bone_graft pool 9,450.000 AED placed on 8 claims by units (26 units; 363.462 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians: claim 2249MF4159-58a8a6 share 75.348 capped at its Dental amount 56.779</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: lab pool 41,042.500 AED placed on 115 claims by units (259 units; 158.465 AED per unit)</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians: claim 2264MF4159-5a1d74 share 150.695 capped at its Dental amount 113.557</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians: claim 2073MF4159-5b1531 share 75.348 capped at its Dental amount 56.779</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians pool 19,515.095 AED placed on 115 claims by units (259 units; 75.348 AED per unit)</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians: claim 2095MF4159-4d3bdb share 75.348 capped at its Dental amount 56.779</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: fils residuals {SWNurs:+34, SWDoc:+10, SWAllied:+16, Pharmacy:+51, MS:-66, GS:+52, Depreciation:-79, OHF:-1, OHDepreciation:+41, OHC:-58} absorbed by claim index 134</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians: claim 2123MF4159-237d2d share 75.348 capped at its Dental amount 56.779</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: bucket Prosthesis profile SWNurs 3.9%, SWDoc 31.2%, SWAllied 17.5%, Prostheses 46.4%, MS 1.0%</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians: claim 2128MF4159-e95eeb share 75.348 capped at its Dental amount 56.779</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: bucket Dental profile SWNurs 8.2%, SWDoc 40.7%, SWAllied 2.2%, Prostheses 1.5%, MS 4.4%, GS 0.0%, Depreciation 2.1%, OHF 34.8%, OHDepreciation 0.6%, OHC 5.5%</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians: claim 2135MF4159-8747a5 share 150.696 capped at its Dental amount 113.557</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: bucket Imaging profile SWNurs 7.9%, SWDoc 42.0%, SWAllied 4.3%, Prostheses 11.7%, MS 4.0%, Depreciation 1.8%, OHF 28.3%</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians: claim 2175MF4159-57b801 share 75.348 capped at its Dental amount 56.779</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians: claim 2197MF4159-9b3fae share 75.348 capped at its Dental amount 56.779</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians: claim 2212MF4159-1be1ce share 904.174 capped at its Dental amount 788.968</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians: claim 2245MF4159-c3ee38 share 75.348 capped at its Dental amount 56.779</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians: claim 2249MF4159-58a8a6 share 75.348 capped at its Dental amount 56.779</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians: claim 2264MF4159-5a1d74 share 150.695 capped at its Dental amount 113.557</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: dental technicians pool 19,515.095 AED placed on 115 claims by units (259 units; 75.348 AED per unit)</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: fils residuals {SWNurs:+34, SWDoc:+10, SWAllied:+16, Pharmacy:+51, MS:-66, GS:+52, Depreciation:-79, OHF:-1, OHDepreciation:+41, OHC:-58} absorbed by claim index 134</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: bucket Prosthesis profile SWAllied 22.1%, Prostheses 77.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: bucket Dental profile SWNurs 8.4%, SWDoc 46.0%, SWAllied 2.4%, MS 4.4%, GS 0.0%, Depreciation 1.9%, OHF 31.6%, OHDepreciation 0.5%, OHC 4.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: bucket Anaesthesia profile SWNurs 7.5%, SWDoc 79.8%, Pharmacy 12.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: bucket Imaging profile SWNurs 81.5%, Depreciation 18.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CostSubmission_MF4159_2025_M12_PROD.xml: bucket Laboratory profile </t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: bucket Anaesthesia profile SWNurs 11.3%, SWDoc 59.9%, Pharmacy 3.8%, Prostheses 16.7%, MS 5.7%, Depreciation 2.6%</t>
         </is>
       </c>
     </row>

--- a/output/model_reports/Model_Report_2025_M01.xlsx
+++ b/output/model_reports/Model_Report_2025_M01.xlsx
@@ -1032,13 +1032,13 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>18849.353</v>
+        <v>10653.92</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>18849.353</v>
+        <v>10653.92</v>
       </c>
     </row>
     <row r="3">
@@ -1054,13 +1054,13 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>234175.887</v>
+        <v>231860.049</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>130158.78</v>
+        <v>133926.628</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>364334.667</v>
+        <v>365786.677</v>
       </c>
     </row>
     <row r="4">
@@ -1076,13 +1076,13 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>18619.637</v>
+        <v>15115.9</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6279.8</v>
+        <v>2511.952</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>24899.437</v>
+        <v>17627.852</v>
       </c>
     </row>
     <row r="5">
@@ -1142,13 +1142,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>103218.843</v>
+        <v>117233.851</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>103218.843</v>
+        <v>117233.851</v>
       </c>
     </row>
     <row r="8">
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>202921.409</v>
+        <v>202921.41</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>10146.07</v>
+        <v>6087.642</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>152191.057</v>
+        <v>156249.486</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>10146.07</v>
@@ -1307,16 +1307,16 @@
         <v>30438.212</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.04999999778239269</v>
+        <v>0.02999999852159513</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.7500000012320042</v>
+        <v>0.7700000014784049</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.04999999778239269</v>
+        <v>0.04999999753599189</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.1500000032032106</v>
+        <v>0.1500000024640081</v>
       </c>
     </row>
     <row r="4">
@@ -1397,28 +1397,28 @@
         <v>70074.94</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>3503.747</v>
+        <v>0</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>7007.494</v>
+        <v>0</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>3503.747</v>
+        <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>56059.952</v>
+        <v>70074.94</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.09999999999999999</v>
+        <v>0</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.7999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1428,13 +1428,13 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>31662.752</v>
+        <v>31662.751</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1583.138</v>
+        <v>949.883</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>26913.338</v>
+        <v>27546.592</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>1583.138</v>
@@ -1443,16 +1443,16 @@
         <v>1583.138</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.05000001263314067</v>
+        <v>0.03000001484394076</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.8499999621005779</v>
+        <v>0.8699999567314919</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.05000001263314067</v>
+        <v>0.0500000142122837</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.05000001263314067</v>
+        <v>0.0500000142122837</v>
       </c>
     </row>
     <row r="8">
@@ -1536,10 +1536,10 @@
         <v>0</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>119316.941</v>
+        <v>123084.844</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>6279.839</v>
+        <v>2511.936</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>0</v>
@@ -1548,10 +1548,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.9500000000000001</v>
+        <v>0.979999996815205</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.05</v>
+        <v>0.02000000318479503</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>0</v>
@@ -1801,13 +1801,13 @@
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>18849.327</v>
+        <v>10653.897</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>1836.541</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>10146.07</v>
+        <v>6087.642</v>
       </c>
       <c r="E2" s="7" t="n">
         <v>0</v>
@@ -1816,10 +1816,10 @@
         <v>1252</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>3503.747</v>
+        <v>0</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>1583.138</v>
+        <v>949.883</v>
       </c>
       <c r="I2" s="7" t="n">
         <v>0</v>
@@ -1837,28 +1837,28 @@
         <v>0</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>0.09743270940124281</v>
+        <v>0.1723820870428915</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>0.5382722682884116</v>
+        <v>0.5714004931716535</v>
       </c>
       <c r="P2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>0.0664214695835029</v>
+        <v>0.1175156846363354</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>0.1858818089367328</v>
+        <v>0</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.08398909945166741</v>
+        <v>0.08915826762732924</v>
       </c>
       <c r="T2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.02800264433844243</v>
+        <v>0.04954346752179039</v>
       </c>
       <c r="V2" s="4" t="n">
         <v>0</v>
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>364334.681</v>
+        <v>365786.773</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>29384.648</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>152191.057</v>
+        <v>156249.486</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>8178.454</v>
@@ -1892,10 +1892,10 @@
         <v>0</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>7007.494</v>
+        <v>0</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>26913.338</v>
+        <v>27546.592</v>
       </c>
       <c r="I3" s="7" t="n">
         <v>1000</v>
@@ -1904,7 +1904,7 @@
         <v>9500.949000000001</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>119316.941</v>
+        <v>123084.844</v>
       </c>
       <c r="L3" s="7" t="n">
         <v>2524.8</v>
@@ -1913,37 +1913,37 @@
         <v>8317</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>0.08065289837175836</v>
+        <v>0.08033272433281781</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>0.4177232224565522</v>
+        <v>0.4271600219945624</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>0.02244764066256981</v>
+        <v>0.02235852852995316</v>
       </c>
       <c r="Q3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>0.01923367267910463</v>
+        <v>0</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.07386982190696252</v>
+        <v>0.07530778593790213</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>0.00274472909703592</v>
+        <v>0.002733833133982677</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.02607753116975433</v>
+        <v>0.02597400918047958</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0.3274926797320182</v>
+        <v>0.3364934248182889</v>
       </c>
       <c r="W3" s="4" t="n">
-        <v>0.006929892024196292</v>
+        <v>0.006902381896679463</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>0.02282791190004775</v>
+        <v>0.02273729017533392</v>
       </c>
     </row>
     <row r="4">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>24899.473</v>
+        <v>17627.823</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>1836.541</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>3503.747</v>
+        <v>0</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>1583.138</v>
@@ -1980,7 +1980,7 @@
         <v>527.831</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>6279.839</v>
+        <v>2511.936</v>
       </c>
       <c r="L4" s="7" t="n">
         <v>0</v>
@@ -1989,31 +1989,31 @@
         <v>0</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.07375822773437815</v>
+        <v>0.1041842205926393</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0.4074813149659834</v>
+        <v>0.575571356712624</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>0.04105737498942247</v>
+        <v>0.05799394514002098</v>
       </c>
       <c r="Q4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>0.1407157091236429</v>
+        <v>0</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.06358118503150649</v>
+        <v>0.08980904788980465</v>
       </c>
       <c r="T4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>0.02119848078712349</v>
+        <v>0.02994306216938983</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.2522077073679431</v>
+        <v>0.1424983674955211</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>0</v>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>103218.823</v>
+        <v>117233.811</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>3673.081</v>
@@ -2044,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>56059.952</v>
+        <v>70074.94</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>1583.138</v>
@@ -2065,22 +2065,22 @@
         <v>0</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>0.03558537961627406</v>
+        <v>0.03133124282720793</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>0.2948901287122795</v>
+        <v>0.2596368039251066</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.1110692765795246</v>
+        <v>0.09779124215282911</v>
       </c>
       <c r="Q5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>0.5431175280888447</v>
+        <v>0.5977366034786671</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.01533768700307695</v>
+        <v>0.01350410761618932</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>0</v>
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>10146.07</v>
+        <v>6087.642</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>152191.057</v>
+        <v>156249.486</v>
       </c>
       <c r="D3" s="7" t="n">
         <v>10146.07</v>
@@ -2218,13 +2218,13 @@
         <v>30438.212</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>202921.409</v>
+        <v>202921.41</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>202921.41</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.7500000012320042</v>
+        <v>0.7700000014784049</v>
       </c>
     </row>
     <row r="4">
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>3503.747</v>
+        <v>0</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>7007.494</v>
+        <v>0</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3503.747</v>
+        <v>0</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>56059.952</v>
+        <v>70074.94</v>
       </c>
       <c r="F6" s="7" t="n">
         <v>70074.94</v>
@@ -2308,7 +2308,7 @@
         <v>70074.94</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.09999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1583.138</v>
+        <v>949.883</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>26913.338</v>
+        <v>27546.592</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>1583.138</v>
@@ -2330,13 +2330,13 @@
         <v>1583.138</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>31662.752</v>
+        <v>31662.751</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>31662.75</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.8499999621005779</v>
+        <v>0.8699999567314919</v>
       </c>
     </row>
     <row r="8">
@@ -2405,10 +2405,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>119316.941</v>
+        <v>123084.844</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>6279.839</v>
+        <v>2511.936</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
@@ -2420,7 +2420,7 @@
         <v>125596.78</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.9500000000000001</v>
+        <v>0.979999996815205</v>
       </c>
     </row>
     <row r="11">
@@ -2486,16 +2486,16 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>18849.327</v>
+        <v>10653.897</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>364334.681</v>
+        <v>365786.773</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>24899.473</v>
+        <v>17627.823</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>103218.823</v>
+        <v>117233.811</v>
       </c>
       <c r="F13" s="8" t="n">
         <v>511302.304</v>
@@ -2623,13 +2623,13 @@
         <v>18233.212</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>16807.94</v>
+        <v>20454.582</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>32632.213</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>15310.8</v>
+        <v>13806.418</v>
       </c>
       <c r="L2" t="inlineStr"/>
     </row>
@@ -2663,13 +2663,13 @@
         <v>10934.843</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>9875.009</v>
+        <v>12061.978</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>17735.28</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>7486.723</v>
+        <v>6544.666</v>
       </c>
       <c r="L3" t="inlineStr"/>
     </row>
@@ -2703,13 +2703,13 @@
         <v>3649.647</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3485.077</v>
+        <v>4215.007</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>7605.273</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>4081.493</v>
+        <v>3804.244</v>
       </c>
       <c r="L4" t="inlineStr"/>
     </row>
@@ -2743,13 +2743,13 @@
         <v>3647.304</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3387.721</v>
+        <v>4117.182</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>6774.365</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>3292.392</v>
+        <v>2996.875</v>
       </c>
       <c r="L5" t="inlineStr"/>
     </row>
@@ -2783,13 +2783,13 @@
         <v>3646.956</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3373.406</v>
+        <v>4102.797</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>6648.202</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>3174.818</v>
+        <v>2876.6</v>
       </c>
       <c r="L6" t="inlineStr"/>
     </row>
@@ -2823,13 +2823,13 @@
         <v>3645.885</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>3328.236</v>
+        <v>4057.413</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>6243.998</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2814.981</v>
+        <v>2508.395</v>
       </c>
       <c r="L7" t="inlineStr"/>
     </row>
@@ -2863,13 +2863,13 @@
         <v>3061.556</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2867.791</v>
+        <v>3480.102</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>6122.045</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>3174.638</v>
+        <v>2936.036</v>
       </c>
       <c r="L8" t="inlineStr"/>
     </row>
@@ -2903,13 +2903,13 @@
         <v>2661.555</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2865.518</v>
+        <v>3397.829</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>3667.782</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>2113.596</v>
+        <v>1891.74</v>
       </c>
       <c r="L9" t="inlineStr"/>
     </row>
@@ -2943,13 +2943,13 @@
         <v>2235.628</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>3016.762</v>
+        <v>3463.887</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>8964.673000000001</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>8982.569</v>
+        <v>8968.51</v>
       </c>
       <c r="L10" t="inlineStr"/>
     </row>
@@ -2983,13 +2983,13 @@
         <v>939.573</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1312.081</v>
+        <v>1499.996</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>4054.36</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>4107.195</v>
+        <v>4109.287</v>
       </c>
       <c r="L11" t="inlineStr"/>
     </row>
@@ -3023,13 +3023,13 @@
         <v>787.827</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>952.566</v>
+        <v>1110.132</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>2424.419</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>2318.077</v>
+        <v>2292.888</v>
       </c>
       <c r="L12" t="inlineStr"/>
     </row>
@@ -3063,13 +3063,13 @@
         <v>777.678</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>841.212</v>
+        <v>996.748</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1465.633</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1155.567</v>
+        <v>1103.606</v>
       </c>
       <c r="L13" t="inlineStr"/>
     </row>
@@ -3103,13 +3103,13 @@
         <v>697.468</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1640.405</v>
+        <v>1779.898</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>6812.267</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>7587.009</v>
+        <v>7698.729</v>
       </c>
       <c r="L14" t="inlineStr"/>
     </row>
@@ -3143,13 +3143,13 @@
         <v>677.96</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1014.756</v>
+        <v>1150.348</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>1509.059</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>769.27</v>
+        <v>718.367</v>
       </c>
       <c r="L15" t="inlineStr"/>
     </row>
@@ -3183,13 +3183,13 @@
         <v>657.741</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>782.0599999999999</v>
+        <v>913.6079999999999</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>2246.368</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1626.919</v>
+        <v>1598.149</v>
       </c>
       <c r="L16" t="inlineStr"/>
     </row>
@@ -3223,13 +3223,13 @@
         <v>597.723</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1018.817</v>
+        <v>1138.361</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>5017.485</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>4151.76</v>
+        <v>4187.996</v>
       </c>
       <c r="L17" t="inlineStr"/>
     </row>
@@ -3263,13 +3263,13 @@
         <v>530.367</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>424.294</v>
+        <v>530.367</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>413.686</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>53.037</v>
+        <v>0</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -3307,13 +3307,13 @@
         <v>418.481</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>984.242</v>
+        <v>1067.938</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>4087.36</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>4552.206</v>
+        <v>4619.238</v>
       </c>
       <c r="L19" t="inlineStr"/>
     </row>
@@ -3347,13 +3347,13 @@
         <v>406.554</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>600.601</v>
+        <v>681.9109999999999</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>827.372</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>386.074</v>
+        <v>353.75</v>
       </c>
       <c r="L20" t="inlineStr"/>
     </row>
@@ -3387,13 +3387,13 @@
         <v>356.026</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>386.863</v>
+        <v>458.068</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>717.511</v>
+        <v>698.304</v>
       </c>
       <c r="L21" t="inlineStr"/>
     </row>
@@ -3427,13 +3427,13 @@
         <v>356.026</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>386.863</v>
+        <v>458.068</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>717.511</v>
+        <v>698.304</v>
       </c>
       <c r="L22" t="inlineStr"/>
     </row>
@@ -3467,13 +3467,13 @@
         <v>279.968</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>721.438</v>
+        <v>777.432</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>3045.591</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>3327.504</v>
+        <v>3378.951</v>
       </c>
       <c r="L23" t="inlineStr"/>
     </row>
@@ -3507,13 +3507,13 @@
         <v>265.183</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>212.146</v>
+        <v>265.183</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>206.842</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>26.519</v>
+        <v>0</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -3551,13 +3551,13 @@
         <v>265.183</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>212.146</v>
+        <v>265.183</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>206.842</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>26.519</v>
+        <v>0</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -3595,13 +3595,13 @@
         <v>265.183</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>212.146</v>
+        <v>265.183</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>206.842</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>26.519</v>
+        <v>0</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -3639,13 +3639,13 @@
         <v>265.183</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>212.146</v>
+        <v>265.183</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>206.842</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>26.519</v>
+        <v>0</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -3683,13 +3683,13 @@
         <v>265.183</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>212.146</v>
+        <v>265.183</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>206.842</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>26.519</v>
+        <v>0</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -3727,13 +3727,13 @@
         <v>265.183</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>212.146</v>
+        <v>265.183</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>206.842</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>26.519</v>
+        <v>0</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -3771,13 +3771,13 @@
         <v>212.712</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>603.782</v>
+        <v>646.325</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>3025.502</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>3488.909</v>
+        <v>3551.253</v>
       </c>
       <c r="L30" t="inlineStr"/>
     </row>
@@ -3811,13 +3811,13 @@
         <v>211.641</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>587.37</v>
+        <v>629.698</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>2745.05</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>3087.994</v>
+        <v>3140.667</v>
       </c>
       <c r="L31" t="inlineStr"/>
     </row>
@@ -3851,13 +3851,13 @@
         <v>210.014</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>516.0309999999999</v>
+        <v>558.034</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>2266.489</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>2549.288</v>
+        <v>2588.784</v>
       </c>
       <c r="L32" t="inlineStr"/>
     </row>
@@ -3891,13 +3891,13 @@
         <v>141.83</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>403.239</v>
+        <v>431.605</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>2023.697</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>2333.427</v>
+        <v>2375.137</v>
       </c>
       <c r="L33" t="inlineStr"/>
     </row>
@@ -3931,13 +3931,13 @@
         <v>141.83</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>403.239</v>
+        <v>431.605</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>2023.697</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>2333.427</v>
+        <v>2375.137</v>
       </c>
       <c r="L34" t="inlineStr"/>
     </row>
@@ -3971,13 +3971,13 @@
         <v>141.829</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>403.238</v>
+        <v>431.604</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>2023.697</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>2333.428</v>
+        <v>2375.138</v>
       </c>
       <c r="L35" t="inlineStr"/>
     </row>
@@ -4011,13 +4011,13 @@
         <v>141.184</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>382.577</v>
+        <v>410.814</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>1843.427</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>2107.899</v>
+        <v>2144.141</v>
       </c>
       <c r="L36" t="inlineStr"/>
     </row>
@@ -4051,13 +4051,13 @@
         <v>140.758</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>386.076</v>
+        <v>414.228</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>1743.247</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1933.621</v>
+        <v>1965.694</v>
       </c>
       <c r="L37" t="inlineStr"/>
     </row>
@@ -4091,13 +4091,13 @@
         <v>140.693</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>383.97</v>
+        <v>412.108</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>1723.157</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1911.093</v>
+        <v>1942.713</v>
       </c>
       <c r="L38" t="inlineStr"/>
     </row>
@@ -4131,13 +4131,13 @@
         <v>140.629</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>381.865</v>
+        <v>409.991</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>1703.067</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1888.565</v>
+        <v>1919.729</v>
       </c>
       <c r="L39" t="inlineStr"/>
     </row>
@@ -4171,13 +4171,13 @@
         <v>140.475</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>359.761</v>
+        <v>387.856</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>1643.065</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1859.911</v>
+        <v>1890.242</v>
       </c>
       <c r="L40" t="inlineStr"/>
     </row>
@@ -4211,13 +4211,13 @@
         <v>140.475</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>374.954</v>
+        <v>403.049</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>1660.745</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1837.384</v>
+        <v>1867.167</v>
       </c>
       <c r="L41" t="inlineStr"/>
     </row>
@@ -4251,13 +4251,13 @@
         <v>140.41</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>372.847</v>
+        <v>400.929</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>1640.656</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>1814.86</v>
+        <v>1844.187</v>
       </c>
       <c r="L42" t="inlineStr"/>
     </row>
@@ -4291,13 +4291,13 @@
         <v>140.41</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>357.61</v>
+        <v>385.692</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>1622.976</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1837.45</v>
+        <v>1867.335</v>
       </c>
       <c r="L43" t="inlineStr"/>
     </row>
@@ -4331,13 +4331,13 @@
         <v>140.41</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>357.61</v>
+        <v>385.692</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>1622.976</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1837.45</v>
+        <v>1867.335</v>
       </c>
       <c r="L44" t="inlineStr"/>
     </row>
@@ -4371,13 +4371,13 @@
         <v>140.409</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>357.609</v>
+        <v>385.691</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>1622.976</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1837.451</v>
+        <v>1867.336</v>
       </c>
       <c r="L45" t="inlineStr"/>
     </row>
@@ -4411,13 +4411,13 @@
         <v>139.623</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>362.011</v>
+        <v>389.935</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>1442.705</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1518.393</v>
+        <v>1540.567</v>
       </c>
       <c r="L46" t="inlineStr"/>
     </row>
@@ -4451,13 +4451,13 @@
         <v>139.557</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>359.887</v>
+        <v>387.799</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>1422.616</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>1495.896</v>
+        <v>1517.604</v>
       </c>
       <c r="L47" t="inlineStr"/>
     </row>
@@ -4491,13 +4491,13 @@
         <v>139.557</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>359.887</v>
+        <v>387.799</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>1422.616</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1495.896</v>
+        <v>1517.604</v>
       </c>
       <c r="L48" t="inlineStr"/>
     </row>
@@ -4531,13 +4531,13 @@
         <v>139.493</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>328.08</v>
+        <v>355.978</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>1362.453</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1517.402</v>
+        <v>1539.746</v>
       </c>
       <c r="L49" t="inlineStr"/>
     </row>
@@ -4571,13 +4571,13 @@
         <v>138.989</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>337.727</v>
+        <v>365.525</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>1257.613</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1303.301</v>
+        <v>1320.424</v>
       </c>
       <c r="L50" t="inlineStr"/>
     </row>
@@ -4611,13 +4611,13 @@
         <v>137.26</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>270.904</v>
+        <v>298.356</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>887.725</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>715.107</v>
+        <v>718.3200000000001</v>
       </c>
       <c r="L51" t="inlineStr"/>
     </row>
@@ -4651,13 +4651,13 @@
         <v>136.379</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>234.022</v>
+        <v>261.298</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>576.775</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>419.962</v>
+        <v>416.062</v>
       </c>
       <c r="L52" t="inlineStr"/>
     </row>
@@ -4691,13 +4691,13 @@
         <v>135.518</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>200.2</v>
+        <v>227.303</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>275.79</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>128.691</v>
+        <v>117.916</v>
       </c>
       <c r="L53" t="inlineStr"/>
     </row>
@@ -4731,13 +4731,13 @@
         <v>135.518</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>200.2</v>
+        <v>227.303</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>275.79</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>128.691</v>
+        <v>117.916</v>
       </c>
       <c r="L54" t="inlineStr"/>
     </row>
@@ -4771,13 +4771,13 @@
         <v>135.517</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>200.199</v>
+        <v>227.303</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>275.79</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>128.692</v>
+        <v>117.916</v>
       </c>
       <c r="L55" t="inlineStr"/>
     </row>
@@ -4811,13 +4811,13 @@
         <v>72.57299999999999</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>267.015</v>
+        <v>281.529</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>1560.564</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1725.561</v>
+        <v>1759.506</v>
       </c>
       <c r="L56" t="inlineStr"/>
     </row>
@@ -4851,13 +4851,13 @@
         <v>72.283</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>255.113</v>
+        <v>269.57</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>1462.795</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1628.537</v>
+        <v>1660.105</v>
       </c>
       <c r="L57" t="inlineStr"/>
     </row>
@@ -4891,13 +4891,13 @@
         <v>71.366</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>221.15</v>
+        <v>235.423</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>1167.21</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1317.142</v>
+        <v>1341.504</v>
       </c>
       <c r="L58" t="inlineStr"/>
     </row>
@@ -4931,13 +4931,13 @@
         <v>71.309</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>216.013</v>
+        <v>230.275</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>1172.164</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1302.234</v>
+        <v>1326.211</v>
       </c>
       <c r="L59" t="inlineStr"/>
     </row>
@@ -4971,13 +4971,13 @@
         <v>71.03400000000001</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>205.588</v>
+        <v>219.795</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>1048.871</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1208.103</v>
+        <v>1229.778</v>
       </c>
       <c r="L60" t="inlineStr"/>
     </row>
@@ -5011,13 +5011,13 @@
         <v>70.947</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>202.696</v>
+        <v>216.886</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1177.943</v>
+        <v>1199.02</v>
       </c>
       <c r="L61" t="inlineStr"/>
     </row>
@@ -5051,13 +5051,13 @@
         <v>70.947</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>202.696</v>
+        <v>216.886</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1177.943</v>
+        <v>1199.02</v>
       </c>
       <c r="L62" t="inlineStr"/>
     </row>
@@ -5091,13 +5091,13 @@
         <v>70.947</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>202.696</v>
+        <v>216.886</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1177.943</v>
+        <v>1199.02</v>
       </c>
       <c r="L63" t="inlineStr"/>
     </row>
@@ -5131,13 +5131,13 @@
         <v>70.947</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>202.696</v>
+        <v>216.886</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1177.943</v>
+        <v>1199.02</v>
       </c>
       <c r="L64" t="inlineStr"/>
     </row>
@@ -5171,13 +5171,13 @@
         <v>70.947</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>202.696</v>
+        <v>216.886</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1177.943</v>
+        <v>1199.02</v>
       </c>
       <c r="L65" t="inlineStr"/>
     </row>
@@ -5211,13 +5211,13 @@
         <v>70.947</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>202.696</v>
+        <v>216.886</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1177.943</v>
+        <v>1199.02</v>
       </c>
       <c r="L66" t="inlineStr"/>
     </row>
@@ -5251,13 +5251,13 @@
         <v>70.947</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>202.696</v>
+        <v>216.886</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1177.943</v>
+        <v>1199.02</v>
       </c>
       <c r="L67" t="inlineStr"/>
     </row>
@@ -5291,13 +5291,13 @@
         <v>70.947</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>202.696</v>
+        <v>216.886</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1177.943</v>
+        <v>1199.02</v>
       </c>
       <c r="L68" t="inlineStr"/>
     </row>
@@ -5331,13 +5331,13 @@
         <v>70.947</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>202.696</v>
+        <v>216.886</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1177.943</v>
+        <v>1199.02</v>
       </c>
       <c r="L69" t="inlineStr"/>
     </row>
@@ -5371,13 +5371,13 @@
         <v>70.947</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>202.696</v>
+        <v>216.886</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1177.943</v>
+        <v>1199.02</v>
       </c>
       <c r="L70" t="inlineStr"/>
     </row>
@@ -5411,13 +5411,13 @@
         <v>70.947</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>202.696</v>
+        <v>216.886</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1177.943</v>
+        <v>1199.02</v>
       </c>
       <c r="L71" t="inlineStr"/>
     </row>
@@ -5451,13 +5451,13 @@
         <v>70.947</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>202.695</v>
+        <v>216.885</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1177.943</v>
+        <v>1199.02</v>
       </c>
       <c r="L72" t="inlineStr"/>
     </row>
@@ -5491,13 +5491,13 @@
         <v>70.947</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>202.695</v>
+        <v>216.885</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1177.943</v>
+        <v>1199.02</v>
       </c>
       <c r="L73" t="inlineStr"/>
     </row>
@@ -5531,13 +5531,13 @@
         <v>70.947</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>202.696</v>
+        <v>216.886</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1177.943</v>
+        <v>1199.02</v>
       </c>
       <c r="L74" t="inlineStr"/>
     </row>
@@ -5571,13 +5571,13 @@
         <v>70.947</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>202.695</v>
+        <v>216.885</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>1177.943</v>
+        <v>1199.02</v>
       </c>
       <c r="L75" t="inlineStr"/>
     </row>
@@ -5611,13 +5611,13 @@
         <v>70.947</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>202.695</v>
+        <v>216.885</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1177.943</v>
+        <v>1199.02</v>
       </c>
       <c r="L76" t="inlineStr"/>
     </row>
@@ -5651,13 +5651,13 @@
         <v>70.947</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>202.695</v>
+        <v>216.885</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1177.943</v>
+        <v>1199.02</v>
       </c>
       <c r="L77" t="inlineStr"/>
     </row>
@@ -5691,13 +5691,13 @@
         <v>70.947</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>202.695</v>
+        <v>216.885</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>1177.943</v>
+        <v>1199.02</v>
       </c>
       <c r="L78" t="inlineStr"/>
     </row>
@@ -5731,13 +5731,13 @@
         <v>70.947</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>202.696</v>
+        <v>216.886</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>1177.943</v>
+        <v>1199.02</v>
       </c>
       <c r="L79" t="inlineStr"/>
     </row>
@@ -5771,13 +5771,13 @@
         <v>70.947</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>202.696</v>
+        <v>216.886</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>1021.893</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>1177.943</v>
+        <v>1199.02</v>
       </c>
       <c r="L80" t="inlineStr"/>
     </row>
@@ -5811,13 +5811,13 @@
         <v>70.88200000000001</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>200.542</v>
+        <v>214.719</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>1001.804</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1155.484</v>
+        <v>1176.117</v>
       </c>
       <c r="L81" t="inlineStr"/>
     </row>
@@ -5851,13 +5851,13 @@
         <v>70.592</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>196.081</v>
+        <v>210.199</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>946.758</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1046.845</v>
+        <v>1064.85</v>
       </c>
       <c r="L82" t="inlineStr"/>
     </row>
@@ -5891,13 +5891,13 @@
         <v>70.53</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>210.627</v>
+        <v>224.733</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>972.247</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>1000.474</v>
+        <v>1017.262</v>
       </c>
       <c r="L83" t="inlineStr"/>
     </row>
@@ -5931,13 +5931,13 @@
         <v>70.23699999999999</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>179.88</v>
+        <v>193.928</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>929.956</v>
+        <v>945.122</v>
       </c>
       <c r="L84" t="inlineStr"/>
     </row>
@@ -5971,13 +5971,13 @@
         <v>70.23699999999999</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>179.88</v>
+        <v>193.928</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>929.956</v>
+        <v>945.122</v>
       </c>
       <c r="L85" t="inlineStr"/>
     </row>
@@ -6011,13 +6011,13 @@
         <v>70.23699999999999</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>179.88</v>
+        <v>193.928</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>929.956</v>
+        <v>945.122</v>
       </c>
       <c r="L86" t="inlineStr"/>
     </row>
@@ -6051,13 +6051,13 @@
         <v>70.23699999999999</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>179.88</v>
+        <v>193.928</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>929.956</v>
+        <v>945.122</v>
       </c>
       <c r="L87" t="inlineStr"/>
     </row>
@@ -6091,13 +6091,13 @@
         <v>70.23699999999999</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>179.88</v>
+        <v>193.928</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>929.956</v>
+        <v>945.122</v>
       </c>
       <c r="L88" t="inlineStr"/>
     </row>
@@ -6131,13 +6131,13 @@
         <v>70.23699999999999</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>179.879</v>
+        <v>193.927</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>929.957</v>
+        <v>945.123</v>
       </c>
       <c r="L89" t="inlineStr"/>
     </row>
@@ -6171,13 +6171,13 @@
         <v>70.23699999999999</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>179.879</v>
+        <v>193.927</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>929.957</v>
+        <v>945.123</v>
       </c>
       <c r="L90" t="inlineStr"/>
     </row>
@@ -6211,13 +6211,13 @@
         <v>70.23699999999999</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>179.879</v>
+        <v>193.927</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>929.957</v>
+        <v>945.123</v>
       </c>
       <c r="L91" t="inlineStr"/>
     </row>
@@ -6251,13 +6251,13 @@
         <v>70.23699999999999</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>179.88</v>
+        <v>193.928</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>929.956</v>
+        <v>945.122</v>
       </c>
       <c r="L92" t="inlineStr"/>
     </row>
@@ -6291,13 +6291,13 @@
         <v>70.23699999999999</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>179.88</v>
+        <v>193.928</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>929.956</v>
+        <v>945.122</v>
       </c>
       <c r="L93" t="inlineStr"/>
     </row>
@@ -6331,13 +6331,13 @@
         <v>70.23699999999999</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>179.88</v>
+        <v>193.928</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>821.533</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>929.956</v>
+        <v>945.122</v>
       </c>
       <c r="L94" t="inlineStr"/>
     </row>
@@ -6371,13 +6371,13 @@
         <v>70.173</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>177.729</v>
+        <v>191.764</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>801.444</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>907.494</v>
+        <v>922.2140000000001</v>
       </c>
       <c r="L95" t="inlineStr"/>
     </row>
@@ -6411,13 +6411,13 @@
         <v>69.86</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>168.207</v>
+        <v>182.179</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>728.371</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>797.71</v>
+        <v>809.7910000000001</v>
       </c>
       <c r="L96" t="inlineStr"/>
     </row>
@@ -6451,13 +6451,13 @@
         <v>69.81100000000001</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>181.005</v>
+        <v>194.967</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>721.353</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>759.197</v>
+        <v>770.284</v>
       </c>
       <c r="L97" t="inlineStr"/>
     </row>
@@ -6491,13 +6491,13 @@
         <v>69.81100000000001</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>181.005</v>
+        <v>194.967</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>721.353</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>759.197</v>
+        <v>770.284</v>
       </c>
       <c r="L98" t="inlineStr"/>
     </row>
@@ -6531,13 +6531,13 @@
         <v>69.81100000000001</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>181.005</v>
+        <v>194.967</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>721.353</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>759.197</v>
+        <v>770.284</v>
       </c>
       <c r="L99" t="inlineStr"/>
     </row>
@@ -6571,13 +6571,13 @@
         <v>69.81100000000001</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>181.005</v>
+        <v>194.967</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>721.353</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>759.197</v>
+        <v>770.284</v>
       </c>
       <c r="L100" t="inlineStr"/>
     </row>
@@ -6611,13 +6611,13 @@
         <v>69.81100000000001</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>181.004</v>
+        <v>194.966</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>721.353</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>759.198</v>
+        <v>770.285</v>
       </c>
       <c r="L101" t="inlineStr"/>
     </row>
@@ -6651,13 +6651,13 @@
         <v>69.81100000000001</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>181.004</v>
+        <v>194.966</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>721.353</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>759.198</v>
+        <v>770.285</v>
       </c>
       <c r="L102" t="inlineStr"/>
     </row>
@@ -6691,13 +6691,13 @@
         <v>69.747</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>164.041</v>
+        <v>177.99</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>681.226</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>758.701</v>
+        <v>769.872</v>
       </c>
       <c r="L103" t="inlineStr"/>
     </row>
@@ -6731,13 +6731,13 @@
         <v>69.747</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>178.883</v>
+        <v>192.832</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>701.2619999999999</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>736.698</v>
+        <v>747.3200000000001</v>
       </c>
       <c r="L104" t="inlineStr"/>
     </row>
@@ -6771,13 +6771,13 @@
         <v>69.747</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>164.04</v>
+        <v>177.989</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>681.226</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>758.702</v>
+        <v>769.873</v>
       </c>
       <c r="L105" t="inlineStr"/>
     </row>
@@ -6811,13 +6811,13 @@
         <v>69.527</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>169.928</v>
+        <v>183.833</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>638.851</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>662.896</v>
+        <v>671.6900000000001</v>
       </c>
       <c r="L106" t="inlineStr"/>
     </row>
@@ -6851,13 +6851,13 @@
         <v>69.527</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>169.927</v>
+        <v>183.832</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>638.851</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>662.896</v>
+        <v>671.691</v>
       </c>
       <c r="L107" t="inlineStr"/>
     </row>
@@ -6891,13 +6891,13 @@
         <v>69.527</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>169.927</v>
+        <v>183.832</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>638.851</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>662.896</v>
+        <v>671.691</v>
       </c>
       <c r="L108" t="inlineStr"/>
     </row>
@@ -6931,13 +6931,13 @@
         <v>69.5</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>167.317</v>
+        <v>181.217</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>720.927</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>654.372</v>
+        <v>662.871</v>
       </c>
       <c r="L109" t="inlineStr"/>
     </row>
@@ -6971,13 +6971,13 @@
         <v>69.14</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>144.069</v>
+        <v>157.897</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>584.207</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>546.828</v>
+        <v>552.854</v>
       </c>
       <c r="L110" t="inlineStr"/>
     </row>
@@ -7011,13 +7011,13 @@
         <v>68.946</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>148.248</v>
+        <v>162.037</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>554.088</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>464.015</v>
+        <v>468.114</v>
       </c>
       <c r="L111" t="inlineStr"/>
     </row>
@@ -7051,13 +7051,13 @@
         <v>68.804</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>142.533</v>
+        <v>156.294</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>503.997</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>416.236</v>
+        <v>419.224</v>
       </c>
       <c r="L112" t="inlineStr"/>
     </row>
@@ -7091,13 +7091,13 @@
         <v>68.64</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>128.021</v>
+        <v>141.749</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>379.829</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>373.353</v>
+        <v>375.243</v>
       </c>
       <c r="L113" t="inlineStr"/>
     </row>
@@ -7131,13 +7131,13 @@
         <v>68.114</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>111.375</v>
+        <v>124.998</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>252.808</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>188.369</v>
+        <v>185.935</v>
       </c>
       <c r="L114" t="inlineStr"/>
     </row>
@@ -7171,13 +7171,13 @@
         <v>68.114</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>114.429</v>
+        <v>128.052</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>263.121</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>183.976</v>
+        <v>181.471</v>
       </c>
       <c r="L115" t="inlineStr"/>
     </row>
@@ -7211,13 +7211,13 @@
         <v>68.107</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>111.131</v>
+        <v>124.753</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>225.004</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>186.627</v>
+        <v>184.11</v>
       </c>
       <c r="L116" t="inlineStr"/>
     </row>
@@ -7251,13 +7251,13 @@
         <v>67.97199999999999</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>108.319</v>
+        <v>121.913</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>213.03</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>136.59</v>
+        <v>132.907</v>
       </c>
       <c r="L117" t="inlineStr"/>
     </row>
@@ -7291,13 +7291,13 @@
         <v>67.97199999999999</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>108.318</v>
+        <v>121.912</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>213.03</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>136.591</v>
+        <v>132.908</v>
       </c>
       <c r="L118" t="inlineStr"/>
     </row>
@@ -7331,13 +7331,13 @@
         <v>67.97199999999999</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>108.572</v>
+        <v>122.166</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>213.03</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>136.305</v>
+        <v>132.65</v>
       </c>
       <c r="L119" t="inlineStr"/>
     </row>
@@ -7371,13 +7371,13 @@
         <v>67.759</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>100.1</v>
+        <v>113.652</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>64.346</v>
+        <v>58.959</v>
       </c>
       <c r="L120" t="inlineStr"/>
     </row>
@@ -7411,13 +7411,13 @@
         <v>67.759</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>100.1</v>
+        <v>113.652</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>64.346</v>
+        <v>58.959</v>
       </c>
       <c r="L121" t="inlineStr"/>
     </row>
@@ -7451,13 +7451,13 @@
         <v>67.759</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>100.1</v>
+        <v>113.652</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>64.346</v>
+        <v>58.959</v>
       </c>
       <c r="L122" t="inlineStr"/>
     </row>
@@ -7491,13 +7491,13 @@
         <v>67.759</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>100.1</v>
+        <v>113.652</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>64.346</v>
+        <v>58.959</v>
       </c>
       <c r="L123" t="inlineStr"/>
     </row>
@@ -7531,13 +7531,13 @@
         <v>67.759</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>100.099</v>
+        <v>113.651</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>64.34699999999999</v>
+        <v>58.96</v>
       </c>
       <c r="L124" t="inlineStr"/>
     </row>
@@ -7571,13 +7571,13 @@
         <v>67.759</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>100.099</v>
+        <v>113.651</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>64.34699999999999</v>
+        <v>58.96</v>
       </c>
       <c r="L125" t="inlineStr"/>
     </row>
@@ -7611,13 +7611,13 @@
         <v>67.759</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>100.099</v>
+        <v>113.651</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>64.34699999999999</v>
+        <v>58.96</v>
       </c>
       <c r="L126" t="inlineStr"/>
     </row>
@@ -7651,13 +7651,13 @@
         <v>67.759</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>100.099</v>
+        <v>113.651</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>64.34699999999999</v>
+        <v>58.96</v>
       </c>
       <c r="L127" t="inlineStr"/>
     </row>
@@ -7691,13 +7691,13 @@
         <v>67.759</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>100.099</v>
+        <v>113.651</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>64.34699999999999</v>
+        <v>58.96</v>
       </c>
       <c r="L128" t="inlineStr"/>
     </row>
@@ -7731,13 +7731,13 @@
         <v>67.759</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>100.099</v>
+        <v>113.651</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>64.34699999999999</v>
+        <v>58.96</v>
       </c>
       <c r="L129" t="inlineStr"/>
     </row>
@@ -7771,13 +7771,13 @@
         <v>67.759</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>100.1</v>
+        <v>113.652</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>64.346</v>
+        <v>58.959</v>
       </c>
       <c r="L130" t="inlineStr"/>
     </row>
@@ -7811,13 +7811,13 @@
         <v>67.759</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>100.1</v>
+        <v>113.652</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>64.346</v>
+        <v>58.959</v>
       </c>
       <c r="L131" t="inlineStr"/>
     </row>
@@ -7851,13 +7851,13 @@
         <v>67.759</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>100.1</v>
+        <v>113.652</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>64.346</v>
+        <v>58.959</v>
       </c>
       <c r="L132" t="inlineStr"/>
     </row>
@@ -7891,13 +7891,13 @@
         <v>67.759</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>100.1</v>
+        <v>113.652</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>137.895</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>64.346</v>
+        <v>58.959</v>
       </c>
       <c r="L133" t="inlineStr"/>
     </row>
@@ -7937,7 +7937,7 @@
         <v>540.143</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>565.776</v>
+        <v>579.018</v>
       </c>
       <c r="L134" t="inlineStr"/>
     </row>
@@ -7977,7 +7977,7 @@
         <v>213.326</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>192.327</v>
+        <v>196.854</v>
       </c>
       <c r="L135" t="inlineStr"/>
     </row>
@@ -8044,7 +8044,7 @@
         <v>1826.525</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1552.786</v>
+        <v>440.718</v>
       </c>
     </row>
     <row r="4">
@@ -8057,7 +8057,7 @@
         <v>5898.341</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>11230.422</v>
+        <v>9607.509</v>
       </c>
     </row>
     <row r="5">
@@ -8070,7 +8070,7 @@
         <v>783.068</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1535.083</v>
+        <v>623.422</v>
       </c>
     </row>
     <row r="6">
@@ -8109,7 +8109,7 @@
         <v>11.862</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>16807.94</v>
+        <v>20454.582</v>
       </c>
     </row>
     <row r="9">
@@ -8135,7 +8135,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4080.378</v>
+        <v>4198.909</v>
       </c>
     </row>
     <row r="11">
@@ -8148,7 +8148,7 @@
         <v>0</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>197.551</v>
+        <v>79.02</v>
       </c>
     </row>
     <row r="12">
@@ -8378,7 +8378,7 @@
         <v>75.13500000000001</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>23.609</v>
+        <v>17.158</v>
       </c>
     </row>
     <row r="30">
@@ -8391,7 +8391,7 @@
         <v>128.363</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>308.201</v>
+        <v>314.652</v>
       </c>
     </row>
     <row r="31">
@@ -8443,7 +8443,7 @@
         <v>0</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>154.174</v>
+        <v>158.642</v>
       </c>
     </row>
     <row r="35">
@@ -8456,7 +8456,7 @@
         <v>0</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>7.446</v>
+        <v>2.978</v>
       </c>
     </row>
     <row r="36">
@@ -8851,28 +8851,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M01_PROD.xml: bucket Prosthesis profile SWNurs 3.6%, SWDoc 29.5%, SWAllied 11.1%, Prostheses 54.3%, MS 1.5%</t>
+          <t>CostSubmission_MF4159_2025_M01_PROD.xml: bucket Prosthesis profile SWNurs 3.1%, SWDoc 26.0%, SWAllied 9.8%, Prostheses 59.8%, MS 1.4%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M01_PROD.xml: bucket Dental profile SWNurs 8.1%, SWDoc 41.8%, SWAllied 2.2%, Prostheses 1.9%, MS 7.4%, GS 0.3%, Depreciation 2.6%, OHF 32.7%, OHDepreciation 0.7%, OHC 2.3%</t>
+          <t>CostSubmission_MF4159_2025_M01_PROD.xml: bucket Dental profile SWNurs 8.0%, SWDoc 42.7%, SWAllied 2.2%, MS 7.5%, GS 0.3%, Depreciation 2.6%, OHF 33.6%, OHDepreciation 0.7%, OHC 2.3%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M01_PROD.xml: bucket Imaging profile SWNurs 7.4%, SWDoc 40.7%, SWAllied 4.1%, Prostheses 14.1%, MS 6.4%, Depreciation 2.1%, OHF 25.2%</t>
+          <t>CostSubmission_MF4159_2025_M01_PROD.xml: bucket Imaging profile SWNurs 10.4%, SWDoc 57.6%, SWAllied 5.8%, MS 9.0%, Depreciation 3.0%, OHF 14.2%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M01_PROD.xml: bucket Anaesthesia profile SWNurs 9.7%, SWDoc 53.8%, Pharmacy 6.6%, Prostheses 18.6%, MS 8.4%, Depreciation 2.8%</t>
+          <t>CostSubmission_MF4159_2025_M01_PROD.xml: bucket Anaesthesia profile SWNurs 17.2%, SWDoc 57.1%, Pharmacy 11.8%, MS 8.9%, Depreciation 5.0%</t>
         </is>
       </c>
     </row>
@@ -8935,28 +8935,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M02_PROD.xml: bucket Prosthesis profile SWNurs 3.1%, SWDoc 37.9%, SWAllied 7.9%, Prostheses 49.6%, MS 1.5%</t>
+          <t>CostSubmission_MF4159_2025_M02_PROD.xml: bucket Prosthesis profile SWNurs 2.8%, SWDoc 33.7%, SWAllied 7.0%, Prostheses 55.2%, MS 1.3%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M02_PROD.xml: bucket Dental profile SWNurs 6.1%, SWDoc 46.0%, SWAllied 1.7%, Prostheses 1.5%, MS 6.1%, GS 0.6%, Depreciation 2.4%, OHF 25.4%, OHDepreciation 0.6%, OHC 9.5%</t>
+          <t>CostSubmission_MF4159_2025_M02_PROD.xml: bucket Dental profile SWNurs 6.1%, SWDoc 46.9%, SWAllied 1.7%, MS 6.2%, GS 0.6%, Depreciation 2.4%, OHF 26.1%, OHDepreciation 0.6%, OHC 9.4%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M02_PROD.xml: bucket Imaging profile SWNurs 6.1%, SWDoc 49.1%, SWAllied 3.4%, Prostheses 12.1%, MS 5.8%, Depreciation 2.2%, OHF 21.4%</t>
+          <t>CostSubmission_MF4159_2025_M02_PROD.xml: bucket Imaging profile SWNurs 8.1%, SWDoc 65.4%, SWAllied 4.5%, MS 7.7%, Depreciation 2.9%, OHF 11.4%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M02_PROD.xml: bucket Anaesthesia profile SWNurs 7.7%, SWDoc 61.6%, Pharmacy 5.6%, Prostheses 15.1%, MS 7.3%, Depreciation 2.7%</t>
+          <t>CostSubmission_MF4159_2025_M02_PROD.xml: bucket Anaesthesia profile SWNurs 13.4%, SWDoc 64.5%, Pharmacy 9.8%, MS 7.6%, Depreciation 4.7%</t>
         </is>
       </c>
     </row>
@@ -9362,28 +9362,28 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: bucket Prosthesis profile SWNurs 2.7%, SWDoc 30.2%, SWAllied 6.9%, Prostheses 58.9%, MS 1.3%</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: bucket Prosthesis profile SWNurs 2.4%, SWDoc 26.4%, SWAllied 6.0%, Prostheses 64.1%, MS 1.1%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: bucket Dental profile SWNurs 5.9%, SWDoc 41.3%, SWAllied 1.7%, Prostheses 2.0%, MS 6.0%, Depreciation 2.2%, OHF 26.1%, OHDepreciation 0.6%, OHC 14.2%</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: bucket Dental profile SWNurs 5.9%, SWDoc 42.4%, SWAllied 1.7%, MS 6.1%, Depreciation 2.2%, OHF 26.9%, OHDepreciation 0.6%, OHC 14.2%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: bucket Imaging profile SWNurs 6.0%, SWDoc 44.5%, SWAllied 3.4%, Prostheses 16.2%, MS 5.7%, Depreciation 1.9%, OHF 22.2%</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: bucket Imaging profile SWNurs 8.5%, SWDoc 63.2%, SWAllied 4.8%, MS 8.1%, Depreciation 2.8%, OHF 12.6%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M03_PROD.xml: bucket Anaesthesia profile SWNurs 7.7%, SWDoc 56.8%, Pharmacy 5.0%, Prostheses 20.7%, MS 7.3%, Depreciation 2.5%</t>
+          <t>CostSubmission_MF4159_2025_M03_PROD.xml: bucket Anaesthesia profile SWNurs 14.3%, SWDoc 63.6%, Pharmacy 9.3%, MS 8.2%, Depreciation 4.6%</t>
         </is>
       </c>
     </row>
@@ -9530,28 +9530,28 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: bucket Prosthesis profile SWNurs 3.7%, SWDoc 27.0%, SWAllied 5.6%, Prostheses 62.0%, MS 1.7%</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: bucket Prosthesis profile SWNurs 3.2%, SWDoc 23.4%, SWAllied 4.9%, Prostheses 67.1%, MS 1.5%</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: bucket Dental profile SWNurs 7.0%, SWDoc 31.7%, SWAllied 1.9%, Prostheses 1.8%, MS 6.8%, GS 0.2%, Depreciation 2.4%, OHF 30.4%, OHDepreciation 0.7%, OHC 17.1%</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: bucket Dental profile SWNurs 7.0%, SWDoc 32.4%, SWAllied 1.8%, MS 6.9%, GS 0.2%, Depreciation 2.4%, OHF 31.4%, OHDepreciation 0.6%, OHC 17.1%</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: bucket Imaging profile SWNurs 7.5%, SWDoc 36.2%, SWAllied 4.0%, Prostheses 15.6%, MS 6.9%, Depreciation 2.3%, OHF 27.5%</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: bucket Imaging profile SWNurs 11.1%, SWDoc 53.4%, SWAllied 5.9%, MS 10.1%, Depreciation 3.4%, OHF 16.2%</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M04_PROD.xml: bucket Anaesthesia profile SWNurs 10.3%, SWDoc 49.5%, Pharmacy 6.4%, Prostheses 21.3%, MS 9.4%, Depreciation 3.2%</t>
+          <t>CostSubmission_MF4159_2025_M04_PROD.xml: bucket Anaesthesia profile SWNurs 18.6%, SWDoc 53.8%, Pharmacy 11.6%, MS 10.2%, Depreciation 5.8%</t>
         </is>
       </c>
     </row>
@@ -9614,28 +9614,28 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M05_PROD.xml: bucket Prosthesis profile SWNurs 4.4%, SWDoc 30.8%, SWAllied 8.8%, Prostheses 54.7%, MS 1.3%</t>
+          <t>CostSubmission_MF4159_2025_M05_PROD.xml: bucket Prosthesis profile SWNurs 3.8%, SWDoc 27.1%, SWAllied 7.7%, Prostheses 60.2%, MS 1.1%</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M05_PROD.xml: bucket Dental profile SWNurs 9.2%, SWDoc 40.6%, SWAllied 2.3%, Prostheses 1.8%, MS 5.8%, Depreciation 2.7%, OHF 36.3%, OHDepreciation 0.7%, OHC 0.7%</t>
+          <t>CostSubmission_MF4159_2025_M05_PROD.xml: bucket Dental profile SWNurs 9.1%, SWDoc 41.4%, SWAllied 2.2%, MS 5.9%, Depreciation 2.7%, OHF 37.2%, OHDepreciation 0.7%, OHC 0.7%</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M05_PROD.xml: bucket Imaging profile SWNurs 8.3%, SWDoc 39.4%, SWAllied 4.1%, Prostheses 13.1%, MS 5.0%, Depreciation 2.2%, OHF 27.8%</t>
+          <t>CostSubmission_MF4159_2025_M05_PROD.xml: bucket Imaging profile SWNurs 11.9%, SWDoc 56.2%, SWAllied 5.8%, MS 7.1%, Depreciation 3.1%, OHF 15.9%</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M05_PROD.xml: bucket Anaesthesia profile SWNurs 11.5%, SWDoc 54.2%, Pharmacy 6.5%, Prostheses 18.0%, MS 6.8%, Depreciation 3.0%</t>
+          <t>CostSubmission_MF4159_2025_M05_PROD.xml: bucket Anaesthesia profile SWNurs 19.9%, SWDoc 56.5%, Pharmacy 11.3%, MS 7.1%, Depreciation 5.2%</t>
         </is>
       </c>
     </row>
@@ -9691,28 +9691,28 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M06_PROD.xml: bucket Prosthesis profile SWNurs 6.9%, SWDoc 40.6%, SWAllied 1.7%, Prostheses 49.4%, MS 1.3%</t>
+          <t>CostSubmission_MF4159_2025_M06_PROD.xml: bucket Prosthesis profile SWNurs 6.1%, SWDoc 36.2%, SWAllied 1.5%, Prostheses 55.0%, MS 1.2%</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M06_PROD.xml: bucket Dental profile SWNurs 9.8%, SWDoc 36.2%, SWAllied 2.5%, Prostheses 1.1%, MS 4.1%, Depreciation 2.0%, OHF 36.0%, OHDepreciation 0.5%, OHC 7.8%</t>
+          <t>CostSubmission_MF4159_2025_M06_PROD.xml: bucket Dental profile SWNurs 9.7%, SWDoc 36.8%, SWAllied 2.4%, MS 4.1%, Depreciation 2.0%, OHF 36.8%, OHDepreciation 0.5%, OHC 7.7%</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M06_PROD.xml: bucket Imaging profile SWNurs 10.0%, SWDoc 39.4%, SWAllied 5.0%, Prostheses 9.0%, MS 3.9%, Depreciation 1.8%, OHF 30.9%</t>
+          <t>CostSubmission_MF4159_2025_M06_PROD.xml: bucket Imaging profile SWNurs 13.8%, SWDoc 54.3%, SWAllied 6.9%, MS 5.4%, Depreciation 2.5%, OHF 17.1%</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M06_PROD.xml: bucket Anaesthesia profile SWNurs 14.9%, SWDoc 58.3%, Pharmacy 5.1%, Prostheses 13.3%, MS 5.8%, Depreciation 2.6%</t>
+          <t>CostSubmission_MF4159_2025_M06_PROD.xml: bucket Anaesthesia profile SWNurs 24.3%, SWDoc 57.3%, Pharmacy 8.3%, MS 5.7%, Depreciation 4.3%</t>
         </is>
       </c>
     </row>
@@ -9817,28 +9817,28 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M07_PROD.xml: bucket Prosthesis profile SWNurs 5.8%, SWDoc 33.0%, SWAllied 10.0%, Prostheses 49.5%, MS 1.7%</t>
+          <t>CostSubmission_MF4159_2025_M07_PROD.xml: bucket Prosthesis profile SWNurs 5.1%, SWDoc 29.4%, SWAllied 8.9%, Prostheses 55.1%, MS 1.5%</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M07_PROD.xml: bucket Dental profile SWNurs 9.5%, SWDoc 33.9%, SWAllied 2.6%, Prostheses 1.3%, MS 6.0%, Depreciation 2.6%, OHF 36.5%, OHDepreciation 0.7%, OHC 6.8%</t>
+          <t>CostSubmission_MF4159_2025_M07_PROD.xml: bucket Dental profile SWNurs 9.4%, SWDoc 34.5%, SWAllied 2.6%, MS 6.1%, Depreciation 2.6%, OHF 37.3%, OHDepreciation 0.7%, OHC 6.8%</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M07_PROD.xml: bucket Imaging profile SWNurs 9.5%, SWDoc 36.2%, SWAllied 5.2%, Prostheses 10.2%, MS 5.7%, Depreciation 2.3%, OHF 30.8%</t>
+          <t>CostSubmission_MF4159_2025_M07_PROD.xml: bucket Imaging profile SWNurs 13.3%, SWDoc 50.8%, SWAllied 7.3%, MS 8.0%, Depreciation 3.2%, OHF 17.3%</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M07_PROD.xml: bucket Anaesthesia profile SWNurs 13.5%, SWDoc 51.4%, Pharmacy 9.3%, Prostheses 14.4%, MS 8.1%, Depreciation 3.3%</t>
+          <t>CostSubmission_MF4159_2025_M07_PROD.xml: bucket Anaesthesia profile SWNurs 21.8%, SWDoc 49.9%, Pharmacy 15.1%, MS 7.8%, Depreciation 5.3%</t>
         </is>
       </c>
     </row>
@@ -9957,28 +9957,28 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: bucket Prosthesis profile SWNurs 4.8%, SWDoc 23.5%, SWAllied 14.0%, Prostheses 56.2%, MS 1.5%</t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: bucket Prosthesis profile SWNurs 4.2%, SWDoc 20.6%, SWAllied 12.3%, Prostheses 61.6%, MS 1.3%</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: bucket Dental profile SWNurs 9.9%, SWDoc 30.3%, SWAllied 2.4%, Prostheses 1.8%, MS 6.7%, Depreciation 2.5%, OHF 38.7%, OHDepreciation 0.7%, OHC 7.1%</t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: bucket Dental profile SWNurs 9.8%, SWDoc 31.0%, SWAllied 2.4%, MS 6.8%, Depreciation 2.5%, OHF 39.8%, OHDepreciation 0.7%, OHC 7.1%</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: bucket Imaging profile SWNurs 9.6%, SWDoc 31.5%, SWAllied 4.6%, Prostheses 14.2%, MS 6.1%, Depreciation 2.1%, OHF 31.8%</t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: bucket Imaging profile SWNurs 14.4%, SWDoc 47.2%, SWAllied 7.0%, MS 9.2%, Depreciation 3.2%, OHF 19.0%</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M08_PROD.xml: bucket Anaesthesia profile SWNurs 13.9%, SWDoc 45.6%, Pharmacy 8.0%, Prostheses 20.5%, MS 8.9%, Depreciation 3.1%</t>
+          <t>CostSubmission_MF4159_2025_M08_PROD.xml: bucket Anaesthesia profile SWNurs 24.1%, SWDoc 47.5%, Pharmacy 13.8%, MS 9.2%, Depreciation 5.4%</t>
         </is>
       </c>
     </row>
@@ -10041,28 +10041,28 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M09_PROD.xml: bucket Prosthesis profile SWNurs 3.5%, SWDoc 29.3%, SWAllied 13.4%, Prostheses 52.3%, MS 1.4%</t>
+          <t>CostSubmission_MF4159_2025_M09_PROD.xml: bucket Prosthesis profile SWNurs 3.1%, SWDoc 25.9%, SWAllied 11.9%, Prostheses 57.8%, MS 1.3%</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M09_PROD.xml: bucket Dental profile SWNurs 6.5%, SWDoc 33.9%, SWAllied 2.4%, Prostheses 1.5%, MS 5.6%, Depreciation 2.5%, OHF 39.5%, OHDepreciation 0.7%, OHC 7.4%</t>
+          <t>CostSubmission_MF4159_2025_M09_PROD.xml: bucket Dental profile SWNurs 6.5%, SWDoc 34.6%, SWAllied 2.4%, MS 5.7%, Depreciation 2.5%, OHF 40.4%, OHDepreciation 0.7%, OHC 7.3%</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M09_PROD.xml: bucket Imaging profile SWNurs 6.5%, SWDoc 36.1%, SWAllied 4.8%, Prostheses 12.1%, MS 5.3%, Depreciation 2.2%, OHF 33.1%</t>
+          <t>CostSubmission_MF4159_2025_M09_PROD.xml: bucket Imaging profile SWNurs 9.5%, SWDoc 53.0%, SWAllied 7.0%, MS 7.8%, Depreciation 3.2%, OHF 19.5%</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M09_PROD.xml: bucket Anaesthesia profile SWNurs 9.1%, SWDoc 50.4%, Pharmacy 13.1%, Prostheses 16.9%, MS 7.4%, Depreciation 3.1%</t>
+          <t>CostSubmission_MF4159_2025_M09_PROD.xml: bucket Anaesthesia profile SWNurs 15.1%, SWDoc 50.4%, Pharmacy 21.9%, MS 7.4%, Depreciation 5.2%</t>
         </is>
       </c>
     </row>
@@ -10125,28 +10125,28 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M10_PROD.xml: bucket Prosthesis profile SWNurs 4.8%, SWDoc 38.3%, SWAllied 9.5%, Prostheses 45.9%, MS 1.4%</t>
+          <t>CostSubmission_MF4159_2025_M10_PROD.xml: bucket Prosthesis profile SWNurs 4.3%, SWDoc 34.4%, SWAllied 8.5%, Prostheses 51.5%, MS 1.3%</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M10_PROD.xml: bucket Dental profile SWNurs 8.0%, SWDoc 39.7%, SWAllied 2.1%, Prostheses 1.2%, MS 5.1%, GS 0.3%, Depreciation 2.3%, OHF 34.5%, OHDepreciation 0.6%, OHC 6.1%</t>
+          <t>CostSubmission_MF4159_2025_M10_PROD.xml: bucket Dental profile SWNurs 7.9%, SWDoc 40.3%, SWAllied 2.1%, MS 5.2%, GS 0.3%, Depreciation 2.3%, OHF 35.3%, OHDepreciation 0.6%, OHC 6.1%</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M10_PROD.xml: bucket Imaging profile SWNurs 8.0%, SWDoc 42.3%, SWAllied 4.2%, Prostheses 9.5%, MS 4.8%, Depreciation 2.0%, OHF 29.1%</t>
+          <t>CostSubmission_MF4159_2025_M10_PROD.xml: bucket Imaging profile SWNurs 10.9%, SWDoc 58.0%, SWAllied 5.8%, MS 6.6%, Depreciation 2.8%, OHF 15.9%</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M10_PROD.xml: bucket Anaesthesia profile SWNurs 11.2%, SWDoc 59.6%, Pharmacy 6.2%, Prostheses 13.4%, MS 6.8%, Depreciation 2.9%</t>
+          <t>CostSubmission_MF4159_2025_M10_PROD.xml: bucket Anaesthesia profile SWNurs 18.7%, SWDoc 59.5%, Pharmacy 10.3%, MS 6.8%, Depreciation 4.8%</t>
         </is>
       </c>
     </row>
@@ -10209,28 +10209,28 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M11_PROD.xml: bucket Prosthesis profile SWNurs 4.7%, SWDoc 28.5%, SWAllied 13.6%, Prostheses 51.7%, MS 1.5%</t>
+          <t>CostSubmission_MF4159_2025_M11_PROD.xml: bucket Prosthesis profile SWNurs 4.1%, SWDoc 25.3%, SWAllied 12.0%, Prostheses 57.2%, MS 1.3%</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M11_PROD.xml: bucket Dental profile SWNurs 8.4%, SWDoc 32.0%, SWAllied 2.2%, Prostheses 1.5%, MS 5.7%, Depreciation 2.6%, OHF 40.3%, OHDepreciation 0.7%, OHC 6.7%</t>
+          <t>CostSubmission_MF4159_2025_M11_PROD.xml: bucket Dental profile SWNurs 8.3%, SWDoc 32.6%, SWAllied 2.2%, MS 5.8%, Depreciation 2.5%, OHF 41.2%, OHDepreciation 0.7%, OHC 6.7%</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M11_PROD.xml: bucket Imaging profile SWNurs 8.4%, SWDoc 34.2%, SWAllied 4.3%, Prostheses 11.6%, MS 5.4%, Depreciation 2.3%, OHF 33.9%</t>
+          <t>CostSubmission_MF4159_2025_M11_PROD.xml: bucket Imaging profile SWNurs 12.3%, SWDoc 50.2%, SWAllied 6.4%, MS 7.9%, Depreciation 3.3%, OHF 19.9%</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M11_PROD.xml: bucket Anaesthesia profile SWNurs 12.5%, SWDoc 51.0%, Pharmacy 7.7%, Prostheses 17.3%, MS 8.1%, Depreciation 3.4%</t>
+          <t>CostSubmission_MF4159_2025_M11_PROD.xml: bucket Anaesthesia profile SWNurs 21.1%, SWDoc 51.8%, Pharmacy 13.1%, MS 8.2%, Depreciation 5.7%</t>
         </is>
       </c>
     </row>
@@ -10370,28 +10370,28 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: bucket Prosthesis profile SWNurs 3.9%, SWDoc 31.2%, SWAllied 17.5%, Prostheses 46.4%, MS 1.0%</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: bucket Prosthesis profile SWNurs 3.5%, SWDoc 27.9%, SWAllied 15.7%, Prostheses 52.0%, MS 0.9%</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: bucket Dental profile SWNurs 8.2%, SWDoc 40.7%, SWAllied 2.2%, Prostheses 1.5%, MS 4.4%, GS 0.0%, Depreciation 2.1%, OHF 34.8%, OHDepreciation 0.6%, OHC 5.5%</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: bucket Dental profile SWNurs 8.1%, SWDoc 41.5%, SWAllied 2.2%, MS 4.4%, GS 0.0%, Depreciation 2.1%, OHF 35.6%, OHDepreciation 0.6%, OHC 5.5%</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: bucket Imaging profile SWNurs 7.9%, SWDoc 42.0%, SWAllied 4.3%, Prostheses 11.7%, MS 4.0%, Depreciation 1.8%, OHF 28.3%</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: bucket Imaging profile SWNurs 11.1%, SWDoc 58.9%, SWAllied 6.1%, MS 5.6%, Depreciation 2.5%, OHF 15.9%</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>CostSubmission_MF4159_2025_M12_PROD.xml: bucket Anaesthesia profile SWNurs 11.3%, SWDoc 59.9%, Pharmacy 3.8%, Prostheses 16.7%, MS 5.7%, Depreciation 2.6%</t>
+          <t>CostSubmission_MF4159_2025_M12_PROD.xml: bucket Anaesthesia profile SWNurs 19.8%, SWDoc 63.1%, Pharmacy 6.7%, MS 6.0%, Depreciation 4.5%</t>
         </is>
       </c>
     </row>
